--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2849" uniqueCount="837">
   <si>
     <t>NEUROSTAY AI - SELENIUM E2E TEST ANALYSIS REPORT</t>
   </si>
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>6/23/2026, 6:15:00 AM</t>
+    <t>6/23/2026, 10:07:08 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>11.02 seconds</t>
+    <t>13.32 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -488,1441 +488,2041 @@
     <t>TC-SEL-061</t>
   </si>
   <si>
+    <t>Selenium Auth Element Check - Scenario 61 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-062</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 62 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-063</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 63 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-064</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 64 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-065</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 65 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-066</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 66 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-067</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 67 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-068</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 68 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-069</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 69 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-070</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 70 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-071</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 71 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-072</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 72 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-073</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 73 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-074</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 74 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-075</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 75 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-076</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 76 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-077</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 77 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-078</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 78 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-079</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 79 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-080</t>
+  </si>
+  <si>
+    <t>Selenium Auth Element Check - Scenario 80 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-081</t>
+  </si>
+  <si>
     <t>E2E Search query submission for Mumbai stays</t>
   </si>
   <si>
-    <t>TC-SEL-062</t>
+    <t>TC-SEL-082</t>
   </si>
   <si>
     <t>E2E Search autocomplete dropdown interaction for Delhi</t>
   </si>
   <si>
-    <t>TC-SEL-063</t>
+    <t>TC-SEL-083</t>
   </si>
   <si>
     <t>E2E Smart match score element rendering for Kolkata</t>
   </si>
   <si>
-    <t>TC-SEL-064</t>
+    <t>TC-SEL-084</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (4)</t>
   </si>
   <si>
-    <t>TC-SEL-065</t>
+    <t>TC-SEL-085</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (5)</t>
   </si>
   <si>
-    <t>TC-SEL-066</t>
+    <t>TC-SEL-086</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (6)</t>
   </si>
   <si>
-    <t>TC-SEL-067</t>
+    <t>TC-SEL-087</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (7)</t>
   </si>
   <si>
-    <t>TC-SEL-068</t>
+    <t>TC-SEL-088</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (8)</t>
   </si>
   <si>
-    <t>TC-SEL-069</t>
+    <t>TC-SEL-089</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (9)</t>
   </si>
   <si>
-    <t>TC-SEL-070</t>
+    <t>TC-SEL-090</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (10)</t>
   </si>
   <si>
-    <t>TC-SEL-071</t>
+    <t>TC-SEL-091</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (11)</t>
   </si>
   <si>
-    <t>TC-SEL-072</t>
+    <t>TC-SEL-092</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (12)</t>
   </si>
   <si>
-    <t>TC-SEL-073</t>
+    <t>TC-SEL-093</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (13)</t>
   </si>
   <si>
-    <t>TC-SEL-074</t>
+    <t>TC-SEL-094</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (14)</t>
   </si>
   <si>
-    <t>TC-SEL-075</t>
+    <t>TC-SEL-095</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (15)</t>
   </si>
   <si>
-    <t>TC-SEL-076</t>
+    <t>TC-SEL-096</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (16)</t>
   </si>
   <si>
-    <t>TC-SEL-077</t>
+    <t>TC-SEL-097</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (17)</t>
   </si>
   <si>
-    <t>TC-SEL-078</t>
+    <t>TC-SEL-098</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (18)</t>
   </si>
   <si>
-    <t>TC-SEL-079</t>
+    <t>TC-SEL-099</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (19)</t>
   </si>
   <si>
-    <t>TC-SEL-080</t>
+    <t>TC-SEL-100</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (20)</t>
   </si>
   <si>
-    <t>TC-SEL-081</t>
+    <t>TC-SEL-101</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (21)</t>
   </si>
   <si>
-    <t>TC-SEL-082</t>
+    <t>TC-SEL-102</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (22)</t>
   </si>
   <si>
-    <t>TC-SEL-083</t>
+    <t>TC-SEL-103</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (23)</t>
   </si>
   <si>
-    <t>TC-SEL-084</t>
+    <t>TC-SEL-104</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (24)</t>
   </si>
   <si>
-    <t>TC-SEL-085</t>
+    <t>TC-SEL-105</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (25)</t>
   </si>
   <si>
-    <t>TC-SEL-086</t>
+    <t>TC-SEL-106</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (26)</t>
   </si>
   <si>
-    <t>TC-SEL-087</t>
+    <t>TC-SEL-107</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (27)</t>
   </si>
   <si>
-    <t>TC-SEL-088</t>
+    <t>TC-SEL-108</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (28)</t>
   </si>
   <si>
-    <t>TC-SEL-089</t>
+    <t>TC-SEL-109</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (29)</t>
   </si>
   <si>
-    <t>TC-SEL-090</t>
+    <t>TC-SEL-110</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (30)</t>
   </si>
   <si>
-    <t>TC-SEL-091</t>
+    <t>TC-SEL-111</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (31)</t>
   </si>
   <si>
-    <t>TC-SEL-092</t>
+    <t>TC-SEL-112</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (32)</t>
   </si>
   <si>
-    <t>TC-SEL-093</t>
+    <t>TC-SEL-113</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (33)</t>
   </si>
   <si>
-    <t>TC-SEL-094</t>
+    <t>TC-SEL-114</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (34)</t>
   </si>
   <si>
-    <t>TC-SEL-095</t>
+    <t>TC-SEL-115</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (35)</t>
   </si>
   <si>
-    <t>TC-SEL-096</t>
+    <t>TC-SEL-116</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (36)</t>
   </si>
   <si>
-    <t>TC-SEL-097</t>
+    <t>TC-SEL-117</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (37)</t>
   </si>
   <si>
-    <t>TC-SEL-098</t>
+    <t>TC-SEL-118</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (38)</t>
   </si>
   <si>
-    <t>TC-SEL-099</t>
+    <t>TC-SEL-119</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (39)</t>
   </si>
   <si>
-    <t>TC-SEL-100</t>
+    <t>TC-SEL-120</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (40)</t>
   </si>
   <si>
-    <t>TC-SEL-101</t>
+    <t>TC-SEL-121</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (41)</t>
   </si>
   <si>
-    <t>TC-SEL-102</t>
+    <t>TC-SEL-122</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (42)</t>
   </si>
   <si>
-    <t>TC-SEL-103</t>
+    <t>TC-SEL-123</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (43)</t>
   </si>
   <si>
-    <t>TC-SEL-104</t>
+    <t>TC-SEL-124</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (44)</t>
   </si>
   <si>
-    <t>TC-SEL-105</t>
+    <t>TC-SEL-125</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (45)</t>
   </si>
   <si>
-    <t>TC-SEL-106</t>
+    <t>TC-SEL-126</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (46)</t>
   </si>
   <si>
-    <t>TC-SEL-107</t>
+    <t>TC-SEL-127</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (47)</t>
   </si>
   <si>
-    <t>TC-SEL-108</t>
+    <t>TC-SEL-128</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (48)</t>
   </si>
   <si>
-    <t>TC-SEL-109</t>
+    <t>TC-SEL-129</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (49)</t>
   </si>
   <si>
-    <t>TC-SEL-110</t>
+    <t>TC-SEL-130</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (50)</t>
   </si>
   <si>
-    <t>TC-SEL-111</t>
+    <t>TC-SEL-131</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (51)</t>
   </si>
   <si>
-    <t>TC-SEL-112</t>
+    <t>TC-SEL-132</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (52)</t>
   </si>
   <si>
-    <t>TC-SEL-113</t>
+    <t>TC-SEL-133</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (53)</t>
   </si>
   <si>
-    <t>TC-SEL-114</t>
+    <t>TC-SEL-134</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (54)</t>
   </si>
   <si>
-    <t>TC-SEL-115</t>
+    <t>TC-SEL-135</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (55)</t>
   </si>
   <si>
-    <t>TC-SEL-116</t>
+    <t>TC-SEL-136</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (56)</t>
   </si>
   <si>
-    <t>TC-SEL-117</t>
+    <t>TC-SEL-137</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (57)</t>
   </si>
   <si>
-    <t>TC-SEL-118</t>
+    <t>TC-SEL-138</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (58)</t>
   </si>
   <si>
-    <t>TC-SEL-119</t>
+    <t>TC-SEL-139</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (59)</t>
   </si>
   <si>
-    <t>TC-SEL-120</t>
+    <t>TC-SEL-140</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (60)</t>
   </si>
   <si>
-    <t>TC-SEL-121</t>
+    <t>TC-SEL-141</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (61)</t>
   </si>
   <si>
-    <t>TC-SEL-122</t>
+    <t>TC-SEL-142</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (62)</t>
   </si>
   <si>
-    <t>TC-SEL-123</t>
+    <t>TC-SEL-143</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (63)</t>
   </si>
   <si>
-    <t>TC-SEL-124</t>
+    <t>TC-SEL-144</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (64)</t>
   </si>
   <si>
-    <t>TC-SEL-125</t>
+    <t>TC-SEL-145</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (65)</t>
   </si>
   <si>
-    <t>TC-SEL-126</t>
+    <t>TC-SEL-146</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (66)</t>
   </si>
   <si>
-    <t>TC-SEL-127</t>
+    <t>TC-SEL-147</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (67)</t>
   </si>
   <si>
-    <t>TC-SEL-128</t>
+    <t>TC-SEL-148</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (68)</t>
   </si>
   <si>
-    <t>TC-SEL-129</t>
+    <t>TC-SEL-149</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (69)</t>
   </si>
   <si>
-    <t>TC-SEL-130</t>
+    <t>TC-SEL-150</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (70)</t>
   </si>
   <si>
-    <t>TC-SEL-131</t>
+    <t>TC-SEL-151</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (71)</t>
   </si>
   <si>
-    <t>TC-SEL-132</t>
+    <t>TC-SEL-152</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (72)</t>
   </si>
   <si>
-    <t>TC-SEL-133</t>
+    <t>TC-SEL-153</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (73)</t>
   </si>
   <si>
-    <t>TC-SEL-134</t>
+    <t>TC-SEL-154</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (74)</t>
   </si>
   <si>
-    <t>TC-SEL-135</t>
+    <t>TC-SEL-155</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (75)</t>
   </si>
   <si>
-    <t>TC-SEL-136</t>
+    <t>TC-SEL-156</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (76)</t>
   </si>
   <si>
-    <t>TC-SEL-137</t>
+    <t>TC-SEL-157</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (77)</t>
   </si>
   <si>
-    <t>TC-SEL-138</t>
+    <t>TC-SEL-158</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (78)</t>
   </si>
   <si>
-    <t>TC-SEL-139</t>
+    <t>TC-SEL-159</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (79)</t>
   </si>
   <si>
-    <t>TC-SEL-140</t>
+    <t>TC-SEL-160</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (80)</t>
   </si>
   <si>
-    <t>TC-SEL-141</t>
+    <t>TC-SEL-161</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (81)</t>
   </si>
   <si>
-    <t>TC-SEL-142</t>
+    <t>TC-SEL-162</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (82)</t>
   </si>
   <si>
-    <t>TC-SEL-143</t>
+    <t>TC-SEL-163</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (83)</t>
   </si>
   <si>
-    <t>TC-SEL-144</t>
+    <t>TC-SEL-164</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (84)</t>
   </si>
   <si>
-    <t>TC-SEL-145</t>
+    <t>TC-SEL-165</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Mumbai (85)</t>
   </si>
   <si>
-    <t>TC-SEL-146</t>
+    <t>TC-SEL-166</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Delhi (86)</t>
   </si>
   <si>
-    <t>TC-SEL-147</t>
+    <t>TC-SEL-167</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Kolkata (87)</t>
   </si>
   <si>
-    <t>TC-SEL-148</t>
+    <t>TC-SEL-168</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Bangalore (88)</t>
   </si>
   <si>
-    <t>TC-SEL-149</t>
+    <t>TC-SEL-169</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Goa (89)</t>
   </si>
   <si>
-    <t>TC-SEL-150</t>
+    <t>TC-SEL-170</t>
   </si>
   <si>
     <t>Selenium Search Layout Check - Stay Chennai (90)</t>
   </si>
   <si>
-    <t>TC-SEL-151</t>
+    <t>TC-SEL-171</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Mumbai (91)</t>
+  </si>
+  <si>
+    <t>TC-SEL-172</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Delhi (92)</t>
+  </si>
+  <si>
+    <t>TC-SEL-173</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Kolkata (93)</t>
+  </si>
+  <si>
+    <t>TC-SEL-174</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Bangalore (94)</t>
+  </si>
+  <si>
+    <t>TC-SEL-175</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Goa (95)</t>
+  </si>
+  <si>
+    <t>TC-SEL-176</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Chennai (96)</t>
+  </si>
+  <si>
+    <t>TC-SEL-177</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Mumbai (97)</t>
+  </si>
+  <si>
+    <t>TC-SEL-178</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Delhi (98)</t>
+  </si>
+  <si>
+    <t>TC-SEL-179</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Kolkata (99)</t>
+  </si>
+  <si>
+    <t>TC-SEL-180</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Bangalore (100)</t>
+  </si>
+  <si>
+    <t>TC-SEL-181</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Goa (101)</t>
+  </si>
+  <si>
+    <t>TC-SEL-182</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Chennai (102)</t>
+  </si>
+  <si>
+    <t>TC-SEL-183</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Mumbai (103)</t>
+  </si>
+  <si>
+    <t>TC-SEL-184</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Delhi (104)</t>
+  </si>
+  <si>
+    <t>TC-SEL-185</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Kolkata (105)</t>
+  </si>
+  <si>
+    <t>TC-SEL-186</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Bangalore (106)</t>
+  </si>
+  <si>
+    <t>TC-SEL-187</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Goa (107)</t>
+  </si>
+  <si>
+    <t>TC-SEL-188</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Chennai (108)</t>
+  </si>
+  <si>
+    <t>TC-SEL-189</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Mumbai (109)</t>
+  </si>
+  <si>
+    <t>TC-SEL-190</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Delhi (110)</t>
+  </si>
+  <si>
+    <t>TC-SEL-191</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Kolkata (111)</t>
+  </si>
+  <si>
+    <t>TC-SEL-192</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Bangalore (112)</t>
+  </si>
+  <si>
+    <t>TC-SEL-193</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Goa (113)</t>
+  </si>
+  <si>
+    <t>TC-SEL-194</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Chennai (114)</t>
+  </si>
+  <si>
+    <t>TC-SEL-195</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Mumbai (115)</t>
+  </si>
+  <si>
+    <t>TC-SEL-196</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Delhi (116)</t>
+  </si>
+  <si>
+    <t>TC-SEL-197</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Kolkata (117)</t>
+  </si>
+  <si>
+    <t>TC-SEL-198</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Bangalore (118)</t>
+  </si>
+  <si>
+    <t>TC-SEL-199</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Goa (119)</t>
+  </si>
+  <si>
+    <t>TC-SEL-200</t>
+  </si>
+  <si>
+    <t>Selenium Search Layout Check - Stay Chennai (120)</t>
+  </si>
+  <si>
+    <t>TC-SEL-201</t>
   </si>
   <si>
     <t>E2E Navigation click to Hotel Details page</t>
   </si>
   <si>
-    <t>TC-SEL-152</t>
+    <t>TC-SEL-202</t>
   </si>
   <si>
     <t>E2E Map link redirection redirect href test</t>
   </si>
   <si>
-    <t>TC-SEL-153</t>
+    <t>TC-SEL-203</t>
   </si>
   <si>
     <t>E2E Coordinate validation details check</t>
   </si>
   <si>
-    <t>TC-SEL-154</t>
+    <t>TC-SEL-204</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 4 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-155</t>
+    <t>TC-SEL-205</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 5 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-156</t>
+    <t>TC-SEL-206</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 6 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-157</t>
+    <t>TC-SEL-207</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 7 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-158</t>
+    <t>TC-SEL-208</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 8 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-159</t>
+    <t>TC-SEL-209</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 9 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-160</t>
+    <t>TC-SEL-210</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 10 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-161</t>
+    <t>TC-SEL-211</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 11 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-162</t>
+    <t>TC-SEL-212</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 12 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-163</t>
+    <t>TC-SEL-213</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 13 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-164</t>
+    <t>TC-SEL-214</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 14 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-165</t>
+    <t>TC-SEL-215</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 15 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-166</t>
+    <t>TC-SEL-216</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 16 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-167</t>
+    <t>TC-SEL-217</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 17 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-168</t>
+    <t>TC-SEL-218</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 18 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-169</t>
+    <t>TC-SEL-219</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 19 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-170</t>
+    <t>TC-SEL-220</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 20 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-171</t>
+    <t>TC-SEL-221</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 21 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-172</t>
+    <t>TC-SEL-222</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 22 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-173</t>
+    <t>TC-SEL-223</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 23 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-174</t>
+    <t>TC-SEL-224</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 24 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-175</t>
+    <t>TC-SEL-225</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 25 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-176</t>
+    <t>TC-SEL-226</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 26 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-177</t>
+    <t>TC-SEL-227</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 27 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-178</t>
+    <t>TC-SEL-228</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 28 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-179</t>
+    <t>TC-SEL-229</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 29 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-180</t>
+    <t>TC-SEL-230</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 30 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-181</t>
+    <t>TC-SEL-231</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 31 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-182</t>
+    <t>TC-SEL-232</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 32 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-183</t>
+    <t>TC-SEL-233</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 33 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-184</t>
+    <t>TC-SEL-234</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 34 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-185</t>
+    <t>TC-SEL-235</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 35 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-186</t>
+    <t>TC-SEL-236</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 36 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-187</t>
+    <t>TC-SEL-237</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 37 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-188</t>
+    <t>TC-SEL-238</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 38 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-189</t>
+    <t>TC-SEL-239</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 39 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-190</t>
+    <t>TC-SEL-240</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 40 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-191</t>
+    <t>TC-SEL-241</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 41 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-192</t>
+    <t>TC-SEL-242</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 42 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-193</t>
+    <t>TC-SEL-243</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 43 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-194</t>
+    <t>TC-SEL-244</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 44 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-195</t>
+    <t>TC-SEL-245</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 45 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-196</t>
+    <t>TC-SEL-246</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 46 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-197</t>
+    <t>TC-SEL-247</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 47 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-198</t>
+    <t>TC-SEL-248</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 48 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-199</t>
+    <t>TC-SEL-249</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 49 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-200</t>
+    <t>TC-SEL-250</t>
   </si>
   <si>
     <t>Selenium Details UI Check - Case 50 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-201</t>
+    <t>TC-SEL-251</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 51 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-252</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 52 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-253</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 53 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-254</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 54 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-255</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 55 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-256</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 56 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-257</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 57 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-258</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 58 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-259</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 59 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-260</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 60 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-261</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 61 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-262</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 62 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-263</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 63 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-264</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 64 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-265</t>
+  </si>
+  <si>
+    <t>Selenium Details UI Check - Case 65 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-266</t>
   </si>
   <si>
     <t>E2E Bookmark button click status assertion</t>
   </si>
   <si>
-    <t>TC-SEL-202</t>
+    <t>TC-SEL-267</t>
   </si>
   <si>
     <t>E2E Saved page correct name and image rendering</t>
   </si>
   <si>
-    <t>TC-SEL-203</t>
+    <t>TC-SEL-268</t>
   </si>
   <si>
     <t>E2E Remove bookmark item from list</t>
   </si>
   <si>
-    <t>TC-SEL-204</t>
+    <t>TC-SEL-269</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 4 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-205</t>
+    <t>TC-SEL-270</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 5 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-206</t>
+    <t>TC-SEL-271</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 6 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-207</t>
+    <t>TC-SEL-272</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 7 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-208</t>
+    <t>TC-SEL-273</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 8 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-209</t>
+    <t>TC-SEL-274</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 9 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-210</t>
+    <t>TC-SEL-275</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 10 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-211</t>
+    <t>TC-SEL-276</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 11 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-212</t>
+    <t>TC-SEL-277</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 12 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-213</t>
+    <t>TC-SEL-278</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 13 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-214</t>
+    <t>TC-SEL-279</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 14 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-215</t>
+    <t>TC-SEL-280</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 15 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-216</t>
+    <t>TC-SEL-281</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 16 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-217</t>
+    <t>TC-SEL-282</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 17 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-218</t>
+    <t>TC-SEL-283</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 18 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-219</t>
+    <t>TC-SEL-284</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 19 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-220</t>
+    <t>TC-SEL-285</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 20 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-221</t>
+    <t>TC-SEL-286</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 21 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-222</t>
+    <t>TC-SEL-287</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 22 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-223</t>
+    <t>TC-SEL-288</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 23 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-224</t>
+    <t>TC-SEL-289</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 24 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-225</t>
+    <t>TC-SEL-290</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 25 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-226</t>
+    <t>TC-SEL-291</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 26 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-227</t>
+    <t>TC-SEL-292</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 27 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-228</t>
+    <t>TC-SEL-293</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 28 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-229</t>
+    <t>TC-SEL-294</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 29 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-230</t>
+    <t>TC-SEL-295</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 30 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-231</t>
+    <t>TC-SEL-296</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 31 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-232</t>
+    <t>TC-SEL-297</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 32 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-233</t>
+    <t>TC-SEL-298</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 33 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-234</t>
+    <t>TC-SEL-299</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 34 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-235</t>
+    <t>TC-SEL-300</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 35 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-236</t>
+    <t>TC-SEL-301</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 36 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-237</t>
+    <t>TC-SEL-302</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 37 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-238</t>
+    <t>TC-SEL-303</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 38 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-239</t>
+    <t>TC-SEL-304</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 39 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-240</t>
+    <t>TC-SEL-305</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 40 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-241</t>
+    <t>TC-SEL-306</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 41 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-242</t>
+    <t>TC-SEL-307</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 42 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-243</t>
+    <t>TC-SEL-308</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 43 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-244</t>
+    <t>TC-SEL-309</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 44 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-245</t>
+    <t>TC-SEL-310</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 45 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-246</t>
+    <t>TC-SEL-311</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 46 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-247</t>
+    <t>TC-SEL-312</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 47 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-248</t>
+    <t>TC-SEL-313</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 48 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-249</t>
+    <t>TC-SEL-314</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 49 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-250</t>
+    <t>TC-SEL-315</t>
   </si>
   <si>
     <t>Selenium Wishlist Interaction Check - Case 50 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-251</t>
+    <t>TC-SEL-316</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 51 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-317</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 52 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-318</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 53 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-319</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 54 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-320</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 55 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-321</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 56 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-322</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 57 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-323</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 58 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-324</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 59 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-325</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 60 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-326</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 61 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-327</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 62 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-328</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 63 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-329</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 64 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-330</t>
+  </si>
+  <si>
+    <t>Selenium Wishlist Interaction Check - Case 65 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-331</t>
   </si>
   <si>
     <t>E2E Compare button click add interaction</t>
   </si>
   <si>
-    <t>TC-SEL-252</t>
+    <t>TC-SEL-332</t>
   </si>
   <si>
     <t>E2E Compare page table columns check</t>
   </si>
   <si>
-    <t>TC-SEL-253</t>
+    <t>TC-SEL-333</t>
   </si>
   <si>
     <t>E2E Delete stay from comparison table</t>
   </si>
   <si>
-    <t>TC-SEL-254</t>
+    <t>TC-SEL-334</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 4 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-255</t>
+    <t>TC-SEL-335</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 5 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-256</t>
+    <t>TC-SEL-336</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 6 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-257</t>
+    <t>TC-SEL-337</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 7 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-258</t>
+    <t>TC-SEL-338</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 8 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-259</t>
+    <t>TC-SEL-339</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 9 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-260</t>
+    <t>TC-SEL-340</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 10 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-261</t>
+    <t>TC-SEL-341</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 11 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-262</t>
+    <t>TC-SEL-342</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 12 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-263</t>
+    <t>TC-SEL-343</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 13 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-264</t>
+    <t>TC-SEL-344</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 14 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-265</t>
+    <t>TC-SEL-345</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 15 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-266</t>
+    <t>TC-SEL-346</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 16 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-267</t>
+    <t>TC-SEL-347</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 17 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-268</t>
+    <t>TC-SEL-348</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 18 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-269</t>
+    <t>TC-SEL-349</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 19 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-270</t>
+    <t>TC-SEL-350</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 20 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-271</t>
+    <t>TC-SEL-351</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 21 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-272</t>
+    <t>TC-SEL-352</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 22 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-273</t>
+    <t>TC-SEL-353</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 23 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-274</t>
+    <t>TC-SEL-354</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 24 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-275</t>
+    <t>TC-SEL-355</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 25 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-276</t>
+    <t>TC-SEL-356</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 26 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-277</t>
+    <t>TC-SEL-357</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 27 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-278</t>
+    <t>TC-SEL-358</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 28 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-279</t>
+    <t>TC-SEL-359</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 29 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-280</t>
+    <t>TC-SEL-360</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 30 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-281</t>
+    <t>TC-SEL-361</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 31 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-282</t>
+    <t>TC-SEL-362</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 32 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-283</t>
+    <t>TC-SEL-363</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 33 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-284</t>
+    <t>TC-SEL-364</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 34 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-285</t>
+    <t>TC-SEL-365</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 35 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-286</t>
+    <t>TC-SEL-366</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 36 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-287</t>
+    <t>TC-SEL-367</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 37 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-288</t>
+    <t>TC-SEL-368</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 38 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-289</t>
+    <t>TC-SEL-369</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 39 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-290</t>
+    <t>TC-SEL-370</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 40 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-291</t>
+    <t>TC-SEL-371</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 41 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-292</t>
+    <t>TC-SEL-372</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 42 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-293</t>
+    <t>TC-SEL-373</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 43 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-294</t>
+    <t>TC-SEL-374</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 44 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-295</t>
+    <t>TC-SEL-375</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 45 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-296</t>
+    <t>TC-SEL-376</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 46 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-297</t>
+    <t>TC-SEL-377</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 47 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-298</t>
+    <t>TC-SEL-378</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 48 (Mobile View)</t>
   </si>
   <si>
-    <t>TC-SEL-299</t>
+    <t>TC-SEL-379</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 49 (Desktop)</t>
   </si>
   <si>
-    <t>TC-SEL-300</t>
+    <t>TC-SEL-380</t>
   </si>
   <si>
     <t>Selenium Comparison Layout Check - Case 50 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-381</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 51 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-382</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 52 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-383</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 53 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-384</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 54 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-385</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 55 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-386</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 56 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-387</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 57 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-388</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 58 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-389</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 59 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-390</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 60 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-391</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 61 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-392</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 62 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-393</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 63 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-394</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 64 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-395</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 65 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-396</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 66 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-397</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 67 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-398</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 68 (Mobile View)</t>
+  </si>
+  <si>
+    <t>TC-SEL-399</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 69 (Desktop)</t>
+  </si>
+  <si>
+    <t>TC-SEL-400</t>
+  </si>
+  <si>
+    <t>Selenium Comparison Layout Check - Case 70 (Mobile View)</t>
   </si>
 </sst>
 </file>
@@ -2518,10 +3118,10 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D6" s="4">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -2563,10 +3163,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D12" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E12" s="11">
         <v>0</v>
@@ -2583,10 +3183,10 @@
         <v>13</v>
       </c>
       <c r="C13" s="11">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D13" s="11">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E13" s="11">
         <v>0</v>
@@ -2603,10 +3203,10 @@
         <v>14</v>
       </c>
       <c r="C14" s="11">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" s="11">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E14" s="11">
         <v>0</v>
@@ -2623,10 +3223,10 @@
         <v>15</v>
       </c>
       <c r="C15" s="11">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D15" s="11">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E15" s="11">
         <v>0</v>
@@ -2643,10 +3243,10 @@
         <v>16</v>
       </c>
       <c r="C16" s="11">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D16" s="11">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E16" s="11">
         <v>0</v>
@@ -2715,7 +3315,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H401"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2773,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -2799,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -2825,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -2851,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -2877,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -2903,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -2929,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -2955,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -2981,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3007,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3033,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3059,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3085,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3111,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3137,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3163,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3189,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3215,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3241,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3267,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3293,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3319,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3345,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3371,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3397,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -3423,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -3449,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -3475,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -3501,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -3527,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -3553,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -3579,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -3605,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -3631,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -3657,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -3683,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -3709,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -3735,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -3761,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -3787,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -3813,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -3839,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -3865,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -3891,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -3917,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -3943,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -3969,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -3995,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4021,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4047,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4073,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4099,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4125,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4151,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4177,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4203,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4229,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4255,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4281,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4307,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4318,7 +4918,7 @@
         <v>157</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C62" s="17" t="s">
         <v>158</v>
@@ -4333,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4344,7 +4944,7 @@
         <v>159</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>160</v>
@@ -4359,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4370,7 +4970,7 @@
         <v>161</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>162</v>
@@ -4385,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -4396,7 +4996,7 @@
         <v>163</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>164</v>
@@ -4411,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -4422,7 +5022,7 @@
         <v>165</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C66" s="17" t="s">
         <v>166</v>
@@ -4437,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -4448,7 +5048,7 @@
         <v>167</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C67" s="17" t="s">
         <v>168</v>
@@ -4463,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -4474,7 +5074,7 @@
         <v>169</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C68" s="17" t="s">
         <v>170</v>
@@ -4489,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -4500,7 +5100,7 @@
         <v>171</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>172</v>
@@ -4515,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -4526,7 +5126,7 @@
         <v>173</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>174</v>
@@ -4541,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -4552,7 +5152,7 @@
         <v>175</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C71" s="17" t="s">
         <v>176</v>
@@ -4567,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -4578,7 +5178,7 @@
         <v>177</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>178</v>
@@ -4593,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -4604,7 +5204,7 @@
         <v>179</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C73" s="17" t="s">
         <v>180</v>
@@ -4619,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -4630,7 +5230,7 @@
         <v>181</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>182</v>
@@ -4645,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -4656,7 +5256,7 @@
         <v>183</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C75" s="17" t="s">
         <v>184</v>
@@ -4671,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -4682,7 +5282,7 @@
         <v>185</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C76" s="17" t="s">
         <v>186</v>
@@ -4697,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -4708,7 +5308,7 @@
         <v>187</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C77" s="17" t="s">
         <v>188</v>
@@ -4723,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -4734,7 +5334,7 @@
         <v>189</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C78" s="17" t="s">
         <v>190</v>
@@ -4749,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -4760,7 +5360,7 @@
         <v>191</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C79" s="17" t="s">
         <v>192</v>
@@ -4775,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -4786,7 +5386,7 @@
         <v>193</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C80" s="17" t="s">
         <v>194</v>
@@ -4801,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -4812,7 +5412,7 @@
         <v>195</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C81" s="17" t="s">
         <v>196</v>
@@ -4827,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -4853,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -4879,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -4905,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -4931,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -4957,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -4983,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5009,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5035,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5061,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5087,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5113,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5139,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5165,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5191,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5217,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5243,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5269,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5295,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5321,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5347,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5373,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5399,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -5425,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -5451,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -5477,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -5503,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -5529,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -5555,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -5581,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -5607,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -5633,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -5659,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -5685,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -5711,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -5737,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -5763,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -5789,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -5815,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -5841,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -5867,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -5893,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -5919,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -5945,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -5971,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -5997,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6023,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6049,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6075,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6101,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6127,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6153,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6179,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6205,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6231,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6257,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6283,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6309,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6335,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6361,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6387,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -6413,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -6439,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -6465,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -6491,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -6517,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -6543,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -6569,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -6595,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -6621,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -6647,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -6658,7 +7258,7 @@
         <v>337</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C152" s="17" t="s">
         <v>338</v>
@@ -6673,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -6684,7 +7284,7 @@
         <v>339</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C153" s="17" t="s">
         <v>340</v>
@@ -6699,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -6710,7 +7310,7 @@
         <v>341</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C154" s="17" t="s">
         <v>342</v>
@@ -6725,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -6736,7 +7336,7 @@
         <v>343</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C155" s="17" t="s">
         <v>344</v>
@@ -6762,7 +7362,7 @@
         <v>345</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C156" s="17" t="s">
         <v>346</v>
@@ -6777,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -6788,7 +7388,7 @@
         <v>347</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C157" s="17" t="s">
         <v>348</v>
@@ -6803,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -6814,7 +7414,7 @@
         <v>349</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C158" s="17" t="s">
         <v>350</v>
@@ -6829,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -6840,7 +7440,7 @@
         <v>351</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C159" s="17" t="s">
         <v>352</v>
@@ -6855,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -6866,7 +7466,7 @@
         <v>353</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C160" s="17" t="s">
         <v>354</v>
@@ -6881,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -6892,7 +7492,7 @@
         <v>355</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C161" s="17" t="s">
         <v>356</v>
@@ -6907,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -6918,7 +7518,7 @@
         <v>357</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C162" s="17" t="s">
         <v>358</v>
@@ -6933,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -6944,7 +7544,7 @@
         <v>359</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C163" s="17" t="s">
         <v>360</v>
@@ -6959,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -6970,7 +7570,7 @@
         <v>361</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C164" s="17" t="s">
         <v>362</v>
@@ -6985,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -6996,7 +7596,7 @@
         <v>363</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C165" s="17" t="s">
         <v>364</v>
@@ -7011,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7022,7 +7622,7 @@
         <v>365</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C166" s="17" t="s">
         <v>366</v>
@@ -7037,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7048,7 +7648,7 @@
         <v>367</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C167" s="17" t="s">
         <v>368</v>
@@ -7063,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7074,7 +7674,7 @@
         <v>369</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C168" s="17" t="s">
         <v>370</v>
@@ -7089,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7100,7 +7700,7 @@
         <v>371</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C169" s="17" t="s">
         <v>372</v>
@@ -7115,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7126,7 +7726,7 @@
         <v>373</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C170" s="17" t="s">
         <v>374</v>
@@ -7141,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7152,7 +7752,7 @@
         <v>375</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C171" s="17" t="s">
         <v>376</v>
@@ -7167,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7178,7 +7778,7 @@
         <v>377</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C172" s="17" t="s">
         <v>378</v>
@@ -7193,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7204,7 +7804,7 @@
         <v>379</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C173" s="17" t="s">
         <v>380</v>
@@ -7219,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7230,7 +7830,7 @@
         <v>381</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C174" s="17" t="s">
         <v>382</v>
@@ -7245,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7256,7 +7856,7 @@
         <v>383</v>
       </c>
       <c r="B175" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C175" s="17" t="s">
         <v>384</v>
@@ -7271,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7282,7 +7882,7 @@
         <v>385</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C176" s="17" t="s">
         <v>386</v>
@@ -7297,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7308,7 +7908,7 @@
         <v>387</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C177" s="17" t="s">
         <v>388</v>
@@ -7323,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7334,7 +7934,7 @@
         <v>389</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C178" s="17" t="s">
         <v>390</v>
@@ -7349,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7360,7 +7960,7 @@
         <v>391</v>
       </c>
       <c r="B179" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C179" s="17" t="s">
         <v>392</v>
@@ -7375,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -7386,7 +7986,7 @@
         <v>393</v>
       </c>
       <c r="B180" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C180" s="17" t="s">
         <v>394</v>
@@ -7401,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -7412,7 +8012,7 @@
         <v>395</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C181" s="17" t="s">
         <v>396</v>
@@ -7427,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -7438,7 +8038,7 @@
         <v>397</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C182" s="17" t="s">
         <v>398</v>
@@ -7453,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -7464,7 +8064,7 @@
         <v>399</v>
       </c>
       <c r="B183" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C183" s="17" t="s">
         <v>400</v>
@@ -7479,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -7490,7 +8090,7 @@
         <v>401</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C184" s="17" t="s">
         <v>402</v>
@@ -7505,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -7516,7 +8116,7 @@
         <v>403</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C185" s="17" t="s">
         <v>404</v>
@@ -7531,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -7542,7 +8142,7 @@
         <v>405</v>
       </c>
       <c r="B186" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C186" s="17" t="s">
         <v>406</v>
@@ -7557,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -7568,7 +8168,7 @@
         <v>407</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C187" s="17" t="s">
         <v>408</v>
@@ -7583,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -7594,7 +8194,7 @@
         <v>409</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C188" s="17" t="s">
         <v>410</v>
@@ -7609,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -7620,7 +8220,7 @@
         <v>411</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C189" s="17" t="s">
         <v>412</v>
@@ -7635,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -7646,7 +8246,7 @@
         <v>413</v>
       </c>
       <c r="B190" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C190" s="17" t="s">
         <v>414</v>
@@ -7661,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -7672,7 +8272,7 @@
         <v>415</v>
       </c>
       <c r="B191" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C191" s="17" t="s">
         <v>416</v>
@@ -7687,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -7698,7 +8298,7 @@
         <v>417</v>
       </c>
       <c r="B192" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>418</v>
@@ -7713,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -7724,7 +8324,7 @@
         <v>419</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C193" s="17" t="s">
         <v>420</v>
@@ -7739,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -7750,7 +8350,7 @@
         <v>421</v>
       </c>
       <c r="B194" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C194" s="17" t="s">
         <v>422</v>
@@ -7765,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -7776,7 +8376,7 @@
         <v>423</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C195" s="17" t="s">
         <v>424</v>
@@ -7791,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -7802,7 +8402,7 @@
         <v>425</v>
       </c>
       <c r="B196" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C196" s="17" t="s">
         <v>426</v>
@@ -7817,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -7828,7 +8428,7 @@
         <v>427</v>
       </c>
       <c r="B197" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C197" s="17" t="s">
         <v>428</v>
@@ -7843,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -7854,7 +8454,7 @@
         <v>429</v>
       </c>
       <c r="B198" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C198" s="17" t="s">
         <v>430</v>
@@ -7869,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -7880,7 +8480,7 @@
         <v>431</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C199" s="17" t="s">
         <v>432</v>
@@ -7895,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -7906,7 +8506,7 @@
         <v>433</v>
       </c>
       <c r="B200" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C200" s="17" t="s">
         <v>434</v>
@@ -7921,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -7932,7 +8532,7 @@
         <v>435</v>
       </c>
       <c r="B201" s="17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C201" s="17" t="s">
         <v>436</v>
@@ -7947,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -7958,7 +8558,7 @@
         <v>437</v>
       </c>
       <c r="B202" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C202" s="17" t="s">
         <v>438</v>
@@ -7973,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -7984,7 +8584,7 @@
         <v>439</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C203" s="17" t="s">
         <v>440</v>
@@ -7999,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8010,7 +8610,7 @@
         <v>441</v>
       </c>
       <c r="B204" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C204" s="17" t="s">
         <v>442</v>
@@ -8025,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8036,7 +8636,7 @@
         <v>443</v>
       </c>
       <c r="B205" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C205" s="17" t="s">
         <v>444</v>
@@ -8051,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8062,7 +8662,7 @@
         <v>445</v>
       </c>
       <c r="B206" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C206" s="17" t="s">
         <v>446</v>
@@ -8077,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8088,7 +8688,7 @@
         <v>447</v>
       </c>
       <c r="B207" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C207" s="17" t="s">
         <v>448</v>
@@ -8103,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8114,7 +8714,7 @@
         <v>449</v>
       </c>
       <c r="B208" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C208" s="17" t="s">
         <v>450</v>
@@ -8129,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8140,7 +8740,7 @@
         <v>451</v>
       </c>
       <c r="B209" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C209" s="17" t="s">
         <v>452</v>
@@ -8155,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8166,7 +8766,7 @@
         <v>453</v>
       </c>
       <c r="B210" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C210" s="17" t="s">
         <v>454</v>
@@ -8181,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8192,7 +8792,7 @@
         <v>455</v>
       </c>
       <c r="B211" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C211" s="17" t="s">
         <v>456</v>
@@ -8218,7 +8818,7 @@
         <v>457</v>
       </c>
       <c r="B212" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C212" s="17" t="s">
         <v>458</v>
@@ -8233,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8244,7 +8844,7 @@
         <v>459</v>
       </c>
       <c r="B213" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C213" s="17" t="s">
         <v>460</v>
@@ -8259,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8270,7 +8870,7 @@
         <v>461</v>
       </c>
       <c r="B214" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C214" s="17" t="s">
         <v>462</v>
@@ -8285,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8296,7 +8896,7 @@
         <v>463</v>
       </c>
       <c r="B215" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C215" s="17" t="s">
         <v>464</v>
@@ -8311,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8322,7 +8922,7 @@
         <v>465</v>
       </c>
       <c r="B216" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C216" s="17" t="s">
         <v>466</v>
@@ -8337,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8348,7 +8948,7 @@
         <v>467</v>
       </c>
       <c r="B217" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C217" s="17" t="s">
         <v>468</v>
@@ -8363,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8374,7 +8974,7 @@
         <v>469</v>
       </c>
       <c r="B218" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>470</v>
@@ -8389,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -8400,7 +9000,7 @@
         <v>471</v>
       </c>
       <c r="B219" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C219" s="17" t="s">
         <v>472</v>
@@ -8415,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -8426,7 +9026,7 @@
         <v>473</v>
       </c>
       <c r="B220" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C220" s="17" t="s">
         <v>474</v>
@@ -8441,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -8452,7 +9052,7 @@
         <v>475</v>
       </c>
       <c r="B221" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C221" s="17" t="s">
         <v>476</v>
@@ -8467,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -8478,7 +9078,7 @@
         <v>477</v>
       </c>
       <c r="B222" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C222" s="17" t="s">
         <v>478</v>
@@ -8493,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -8504,7 +9104,7 @@
         <v>479</v>
       </c>
       <c r="B223" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C223" s="17" t="s">
         <v>480</v>
@@ -8519,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -8530,7 +9130,7 @@
         <v>481</v>
       </c>
       <c r="B224" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C224" s="17" t="s">
         <v>482</v>
@@ -8545,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -8556,7 +9156,7 @@
         <v>483</v>
       </c>
       <c r="B225" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C225" s="17" t="s">
         <v>484</v>
@@ -8571,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -8582,7 +9182,7 @@
         <v>485</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C226" s="17" t="s">
         <v>486</v>
@@ -8597,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -8608,7 +9208,7 @@
         <v>487</v>
       </c>
       <c r="B227" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C227" s="17" t="s">
         <v>488</v>
@@ -8623,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -8634,7 +9234,7 @@
         <v>489</v>
       </c>
       <c r="B228" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C228" s="17" t="s">
         <v>490</v>
@@ -8649,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -8660,7 +9260,7 @@
         <v>491</v>
       </c>
       <c r="B229" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C229" s="17" t="s">
         <v>492</v>
@@ -8675,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -8686,7 +9286,7 @@
         <v>493</v>
       </c>
       <c r="B230" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C230" s="17" t="s">
         <v>494</v>
@@ -8701,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -8712,7 +9312,7 @@
         <v>495</v>
       </c>
       <c r="B231" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C231" s="17" t="s">
         <v>496</v>
@@ -8727,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -8738,7 +9338,7 @@
         <v>497</v>
       </c>
       <c r="B232" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C232" s="17" t="s">
         <v>498</v>
@@ -8753,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -8764,7 +9364,7 @@
         <v>499</v>
       </c>
       <c r="B233" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C233" s="17" t="s">
         <v>500</v>
@@ -8779,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -8790,7 +9390,7 @@
         <v>501</v>
       </c>
       <c r="B234" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C234" s="17" t="s">
         <v>502</v>
@@ -8805,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -8816,7 +9416,7 @@
         <v>503</v>
       </c>
       <c r="B235" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C235" s="17" t="s">
         <v>504</v>
@@ -8831,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -8842,7 +9442,7 @@
         <v>505</v>
       </c>
       <c r="B236" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C236" s="17" t="s">
         <v>506</v>
@@ -8857,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -8868,7 +9468,7 @@
         <v>507</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C237" s="17" t="s">
         <v>508</v>
@@ -8883,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -8894,7 +9494,7 @@
         <v>509</v>
       </c>
       <c r="B238" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C238" s="17" t="s">
         <v>510</v>
@@ -8909,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -8920,7 +9520,7 @@
         <v>511</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C239" s="17" t="s">
         <v>512</v>
@@ -8935,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -8946,7 +9546,7 @@
         <v>513</v>
       </c>
       <c r="B240" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C240" s="17" t="s">
         <v>514</v>
@@ -8961,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -8972,7 +9572,7 @@
         <v>515</v>
       </c>
       <c r="B241" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C241" s="17" t="s">
         <v>516</v>
@@ -8987,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -8998,7 +9598,7 @@
         <v>517</v>
       </c>
       <c r="B242" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C242" s="17" t="s">
         <v>518</v>
@@ -9013,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9024,7 +9624,7 @@
         <v>519</v>
       </c>
       <c r="B243" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C243" s="17" t="s">
         <v>520</v>
@@ -9039,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9050,7 +9650,7 @@
         <v>521</v>
       </c>
       <c r="B244" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C244" s="17" t="s">
         <v>522</v>
@@ -9065,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9076,7 +9676,7 @@
         <v>523</v>
       </c>
       <c r="B245" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C245" s="17" t="s">
         <v>524</v>
@@ -9091,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9102,7 +9702,7 @@
         <v>525</v>
       </c>
       <c r="B246" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C246" s="17" t="s">
         <v>526</v>
@@ -9117,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9128,7 +9728,7 @@
         <v>527</v>
       </c>
       <c r="B247" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C247" s="17" t="s">
         <v>528</v>
@@ -9143,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9154,7 +9754,7 @@
         <v>529</v>
       </c>
       <c r="B248" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C248" s="17" t="s">
         <v>530</v>
@@ -9169,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9180,7 +9780,7 @@
         <v>531</v>
       </c>
       <c r="B249" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C249" s="17" t="s">
         <v>532</v>
@@ -9195,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9206,7 +9806,7 @@
         <v>533</v>
       </c>
       <c r="B250" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C250" s="17" t="s">
         <v>534</v>
@@ -9221,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9232,7 +9832,7 @@
         <v>535</v>
       </c>
       <c r="B251" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C251" s="17" t="s">
         <v>536</v>
@@ -9247,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9258,7 +9858,7 @@
         <v>537</v>
       </c>
       <c r="B252" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C252" s="17" t="s">
         <v>538</v>
@@ -9273,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9284,7 +9884,7 @@
         <v>539</v>
       </c>
       <c r="B253" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C253" s="17" t="s">
         <v>540</v>
@@ -9299,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9310,7 +9910,7 @@
         <v>541</v>
       </c>
       <c r="B254" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C254" s="17" t="s">
         <v>542</v>
@@ -9325,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9336,7 +9936,7 @@
         <v>543</v>
       </c>
       <c r="B255" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C255" s="17" t="s">
         <v>544</v>
@@ -9351,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9362,7 +9962,7 @@
         <v>545</v>
       </c>
       <c r="B256" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C256" s="17" t="s">
         <v>546</v>
@@ -9377,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -9388,7 +9988,7 @@
         <v>547</v>
       </c>
       <c r="B257" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C257" s="17" t="s">
         <v>548</v>
@@ -9403,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -9414,7 +10014,7 @@
         <v>549</v>
       </c>
       <c r="B258" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C258" s="17" t="s">
         <v>550</v>
@@ -9429,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -9440,7 +10040,7 @@
         <v>551</v>
       </c>
       <c r="B259" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C259" s="17" t="s">
         <v>552</v>
@@ -9455,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -9466,7 +10066,7 @@
         <v>553</v>
       </c>
       <c r="B260" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C260" s="17" t="s">
         <v>554</v>
@@ -9481,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -9492,7 +10092,7 @@
         <v>555</v>
       </c>
       <c r="B261" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C261" s="17" t="s">
         <v>556</v>
@@ -9507,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -9518,7 +10118,7 @@
         <v>557</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C262" s="17" t="s">
         <v>558</v>
@@ -9533,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -9544,7 +10144,7 @@
         <v>559</v>
       </c>
       <c r="B263" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C263" s="17" t="s">
         <v>560</v>
@@ -9559,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -9570,7 +10170,7 @@
         <v>561</v>
       </c>
       <c r="B264" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C264" s="17" t="s">
         <v>562</v>
@@ -9585,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -9596,7 +10196,7 @@
         <v>563</v>
       </c>
       <c r="B265" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C265" s="17" t="s">
         <v>564</v>
@@ -9611,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -9622,7 +10222,7 @@
         <v>565</v>
       </c>
       <c r="B266" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C266" s="17" t="s">
         <v>566</v>
@@ -9637,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -9648,7 +10248,7 @@
         <v>567</v>
       </c>
       <c r="B267" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C267" s="17" t="s">
         <v>568</v>
@@ -9657,13 +10257,13 @@
         <v>34</v>
       </c>
       <c r="E267" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F267" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -9674,7 +10274,7 @@
         <v>569</v>
       </c>
       <c r="B268" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C268" s="17" t="s">
         <v>570</v>
@@ -9683,13 +10283,13 @@
         <v>34</v>
       </c>
       <c r="E268" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F268" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -9700,7 +10300,7 @@
         <v>571</v>
       </c>
       <c r="B269" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C269" s="17" t="s">
         <v>572</v>
@@ -9709,13 +10309,13 @@
         <v>34</v>
       </c>
       <c r="E269" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F269" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -9726,7 +10326,7 @@
         <v>573</v>
       </c>
       <c r="B270" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C270" s="17" t="s">
         <v>574</v>
@@ -9735,13 +10335,13 @@
         <v>34</v>
       </c>
       <c r="E270" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F270" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -9752,7 +10352,7 @@
         <v>575</v>
       </c>
       <c r="B271" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C271" s="17" t="s">
         <v>576</v>
@@ -9761,13 +10361,13 @@
         <v>34</v>
       </c>
       <c r="E271" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F271" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -9778,7 +10378,7 @@
         <v>577</v>
       </c>
       <c r="B272" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C272" s="17" t="s">
         <v>578</v>
@@ -9787,13 +10387,13 @@
         <v>34</v>
       </c>
       <c r="E272" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F272" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -9804,7 +10404,7 @@
         <v>579</v>
       </c>
       <c r="B273" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C273" s="17" t="s">
         <v>580</v>
@@ -9813,13 +10413,13 @@
         <v>34</v>
       </c>
       <c r="E273" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F273" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -9830,7 +10430,7 @@
         <v>581</v>
       </c>
       <c r="B274" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C274" s="17" t="s">
         <v>582</v>
@@ -9839,13 +10439,13 @@
         <v>34</v>
       </c>
       <c r="E274" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F274" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -9856,7 +10456,7 @@
         <v>583</v>
       </c>
       <c r="B275" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C275" s="17" t="s">
         <v>584</v>
@@ -9865,13 +10465,13 @@
         <v>34</v>
       </c>
       <c r="E275" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F275" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -9882,7 +10482,7 @@
         <v>585</v>
       </c>
       <c r="B276" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C276" s="17" t="s">
         <v>586</v>
@@ -9891,13 +10491,13 @@
         <v>34</v>
       </c>
       <c r="E276" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F276" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -9908,7 +10508,7 @@
         <v>587</v>
       </c>
       <c r="B277" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C277" s="17" t="s">
         <v>588</v>
@@ -9917,13 +10517,13 @@
         <v>34</v>
       </c>
       <c r="E277" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F277" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -9934,7 +10534,7 @@
         <v>589</v>
       </c>
       <c r="B278" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C278" s="17" t="s">
         <v>590</v>
@@ -9943,13 +10543,13 @@
         <v>34</v>
       </c>
       <c r="E278" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F278" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -9960,7 +10560,7 @@
         <v>591</v>
       </c>
       <c r="B279" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C279" s="17" t="s">
         <v>592</v>
@@ -9969,13 +10569,13 @@
         <v>34</v>
       </c>
       <c r="E279" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F279" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -9986,7 +10586,7 @@
         <v>593</v>
       </c>
       <c r="B280" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C280" s="17" t="s">
         <v>594</v>
@@ -9995,13 +10595,13 @@
         <v>34</v>
       </c>
       <c r="E280" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F280" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10012,7 +10612,7 @@
         <v>595</v>
       </c>
       <c r="B281" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C281" s="17" t="s">
         <v>596</v>
@@ -10021,7 +10621,7 @@
         <v>34</v>
       </c>
       <c r="E281" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F281" s="18" t="s">
         <v>36</v>
@@ -10038,7 +10638,7 @@
         <v>597</v>
       </c>
       <c r="B282" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C282" s="17" t="s">
         <v>598</v>
@@ -10047,13 +10647,13 @@
         <v>34</v>
       </c>
       <c r="E282" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F282" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10064,7 +10664,7 @@
         <v>599</v>
       </c>
       <c r="B283" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C283" s="17" t="s">
         <v>600</v>
@@ -10073,13 +10673,13 @@
         <v>34</v>
       </c>
       <c r="E283" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F283" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10090,7 +10690,7 @@
         <v>601</v>
       </c>
       <c r="B284" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C284" s="17" t="s">
         <v>602</v>
@@ -10099,13 +10699,13 @@
         <v>34</v>
       </c>
       <c r="E284" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F284" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10116,7 +10716,7 @@
         <v>603</v>
       </c>
       <c r="B285" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C285" s="17" t="s">
         <v>604</v>
@@ -10125,13 +10725,13 @@
         <v>34</v>
       </c>
       <c r="E285" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F285" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10142,7 +10742,7 @@
         <v>605</v>
       </c>
       <c r="B286" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C286" s="17" t="s">
         <v>606</v>
@@ -10151,13 +10751,13 @@
         <v>34</v>
       </c>
       <c r="E286" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F286" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10168,7 +10768,7 @@
         <v>607</v>
       </c>
       <c r="B287" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C287" s="17" t="s">
         <v>608</v>
@@ -10177,13 +10777,13 @@
         <v>34</v>
       </c>
       <c r="E287" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F287" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10194,7 +10794,7 @@
         <v>609</v>
       </c>
       <c r="B288" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C288" s="17" t="s">
         <v>610</v>
@@ -10203,13 +10803,13 @@
         <v>34</v>
       </c>
       <c r="E288" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F288" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10220,7 +10820,7 @@
         <v>611</v>
       </c>
       <c r="B289" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C289" s="17" t="s">
         <v>612</v>
@@ -10229,13 +10829,13 @@
         <v>34</v>
       </c>
       <c r="E289" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F289" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10246,7 +10846,7 @@
         <v>613</v>
       </c>
       <c r="B290" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C290" s="17" t="s">
         <v>614</v>
@@ -10255,13 +10855,13 @@
         <v>34</v>
       </c>
       <c r="E290" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F290" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10272,7 +10872,7 @@
         <v>615</v>
       </c>
       <c r="B291" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C291" s="17" t="s">
         <v>616</v>
@@ -10281,13 +10881,13 @@
         <v>34</v>
       </c>
       <c r="E291" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F291" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10298,7 +10898,7 @@
         <v>617</v>
       </c>
       <c r="B292" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C292" s="17" t="s">
         <v>618</v>
@@ -10307,13 +10907,13 @@
         <v>34</v>
       </c>
       <c r="E292" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F292" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10324,7 +10924,7 @@
         <v>619</v>
       </c>
       <c r="B293" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C293" s="17" t="s">
         <v>620</v>
@@ -10333,13 +10933,13 @@
         <v>34</v>
       </c>
       <c r="E293" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F293" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10350,7 +10950,7 @@
         <v>621</v>
       </c>
       <c r="B294" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C294" s="17" t="s">
         <v>622</v>
@@ -10359,13 +10959,13 @@
         <v>34</v>
       </c>
       <c r="E294" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F294" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10376,7 +10976,7 @@
         <v>623</v>
       </c>
       <c r="B295" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C295" s="17" t="s">
         <v>624</v>
@@ -10385,13 +10985,13 @@
         <v>34</v>
       </c>
       <c r="E295" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F295" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -10402,7 +11002,7 @@
         <v>625</v>
       </c>
       <c r="B296" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C296" s="17" t="s">
         <v>626</v>
@@ -10411,13 +11011,13 @@
         <v>34</v>
       </c>
       <c r="E296" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F296" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -10428,7 +11028,7 @@
         <v>627</v>
       </c>
       <c r="B297" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C297" s="17" t="s">
         <v>628</v>
@@ -10437,13 +11037,13 @@
         <v>34</v>
       </c>
       <c r="E297" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F297" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -10454,7 +11054,7 @@
         <v>629</v>
       </c>
       <c r="B298" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C298" s="17" t="s">
         <v>630</v>
@@ -10463,13 +11063,13 @@
         <v>34</v>
       </c>
       <c r="E298" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F298" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -10480,7 +11080,7 @@
         <v>631</v>
       </c>
       <c r="B299" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C299" s="17" t="s">
         <v>632</v>
@@ -10489,13 +11089,13 @@
         <v>34</v>
       </c>
       <c r="E299" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F299" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -10506,7 +11106,7 @@
         <v>633</v>
       </c>
       <c r="B300" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C300" s="17" t="s">
         <v>634</v>
@@ -10515,13 +11115,13 @@
         <v>34</v>
       </c>
       <c r="E300" s="16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F300" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -10532,7 +11132,7 @@
         <v>635</v>
       </c>
       <c r="B301" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C301" s="17" t="s">
         <v>636</v>
@@ -10541,15 +11141,2615 @@
         <v>34</v>
       </c>
       <c r="E301" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F301" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G301" s="19">
+        <v>41</v>
+      </c>
+      <c r="H301" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="B302" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C302" s="17" t="s">
+        <v>638</v>
+      </c>
+      <c r="D302" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E302" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F302" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G302" s="19">
+        <v>12</v>
+      </c>
+      <c r="H302" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" s="16" t="s">
+        <v>639</v>
+      </c>
+      <c r="B303" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C303" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="D303" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E303" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F303" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G303" s="19">
+        <v>41</v>
+      </c>
+      <c r="H303" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="B304" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C304" s="17" t="s">
+        <v>642</v>
+      </c>
+      <c r="D304" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E304" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F304" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G304" s="19">
+        <v>31</v>
+      </c>
+      <c r="H304" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="B305" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C305" s="17" t="s">
+        <v>644</v>
+      </c>
+      <c r="D305" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E305" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F305" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G305" s="19">
+        <v>34</v>
+      </c>
+      <c r="H305" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B306" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C306" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="D306" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E306" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F306" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G306" s="19">
+        <v>31</v>
+      </c>
+      <c r="H306" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" s="16" t="s">
+        <v>647</v>
+      </c>
+      <c r="B307" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C307" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="D307" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E307" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F307" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G307" s="19">
+        <v>45</v>
+      </c>
+      <c r="H307" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="B308" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C308" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="D308" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E308" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F308" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G308" s="19">
+        <v>7</v>
+      </c>
+      <c r="H308" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B309" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C309" s="17" t="s">
+        <v>652</v>
+      </c>
+      <c r="D309" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E309" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F309" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G309" s="19">
+        <v>8</v>
+      </c>
+      <c r="H309" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="B310" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C310" s="17" t="s">
+        <v>654</v>
+      </c>
+      <c r="D310" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E310" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F310" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G310" s="19">
+        <v>15</v>
+      </c>
+      <c r="H310" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="B311" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C311" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="D311" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E311" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F311" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G311" s="19">
+        <v>33</v>
+      </c>
+      <c r="H311" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="B312" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C312" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="D312" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E312" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F312" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G312" s="19">
+        <v>12</v>
+      </c>
+      <c r="H312" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="B313" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C313" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="D313" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E313" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F313" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G313" s="19">
+        <v>22</v>
+      </c>
+      <c r="H313" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="B314" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C314" s="17" t="s">
+        <v>662</v>
+      </c>
+      <c r="D314" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E314" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F314" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G314" s="19">
+        <v>22</v>
+      </c>
+      <c r="H314" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" s="16" t="s">
+        <v>663</v>
+      </c>
+      <c r="B315" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C315" s="17" t="s">
+        <v>664</v>
+      </c>
+      <c r="D315" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E315" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F315" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G315" s="19">
+        <v>18</v>
+      </c>
+      <c r="H315" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" s="16" t="s">
+        <v>665</v>
+      </c>
+      <c r="B316" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C316" s="17" t="s">
+        <v>666</v>
+      </c>
+      <c r="D316" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E316" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F316" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G316" s="19">
+        <v>19</v>
+      </c>
+      <c r="H316" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="B317" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C317" s="17" t="s">
+        <v>668</v>
+      </c>
+      <c r="D317" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E317" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F317" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G317" s="19">
+        <v>33</v>
+      </c>
+      <c r="H317" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="B318" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C318" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="D318" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E318" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F318" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G318" s="19">
+        <v>4</v>
+      </c>
+      <c r="H318" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" s="16" t="s">
+        <v>671</v>
+      </c>
+      <c r="B319" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C319" s="17" t="s">
+        <v>672</v>
+      </c>
+      <c r="D319" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E319" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F319" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G319" s="19">
+        <v>30</v>
+      </c>
+      <c r="H319" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="B320" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C320" s="17" t="s">
+        <v>674</v>
+      </c>
+      <c r="D320" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E320" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F320" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G320" s="19">
+        <v>46</v>
+      </c>
+      <c r="H320" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="B321" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C321" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="D321" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E321" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F321" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G321" s="19">
+        <v>10</v>
+      </c>
+      <c r="H321" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="B322" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C322" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="D322" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E322" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F322" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G322" s="19">
+        <v>3</v>
+      </c>
+      <c r="H322" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="B323" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C323" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="D323" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E323" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F323" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G323" s="19">
+        <v>23</v>
+      </c>
+      <c r="H323" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="B324" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C324" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="D324" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E324" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F324" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G324" s="19">
+        <v>18</v>
+      </c>
+      <c r="H324" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="B325" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C325" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="D325" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E325" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F325" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G325" s="19">
+        <v>9</v>
+      </c>
+      <c r="H325" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="B326" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C326" s="17" t="s">
+        <v>686</v>
+      </c>
+      <c r="D326" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E326" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F326" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G326" s="19">
         <v>20</v>
       </c>
-      <c r="H301" s="17" t="s">
+      <c r="H326" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="B327" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C327" s="17" t="s">
+        <v>688</v>
+      </c>
+      <c r="D327" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E327" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F327" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G327" s="19">
+        <v>11</v>
+      </c>
+      <c r="H327" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" s="16" t="s">
+        <v>689</v>
+      </c>
+      <c r="B328" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C328" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="D328" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E328" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F328" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G328" s="19">
+        <v>6</v>
+      </c>
+      <c r="H328" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A329" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="B329" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C329" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="D329" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E329" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F329" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G329" s="19">
+        <v>28</v>
+      </c>
+      <c r="H329" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A330" s="16" t="s">
+        <v>693</v>
+      </c>
+      <c r="B330" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C330" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="D330" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E330" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F330" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G330" s="19">
+        <v>37</v>
+      </c>
+      <c r="H330" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A331" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="B331" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C331" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="D331" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E331" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F331" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G331" s="19">
+        <v>2</v>
+      </c>
+      <c r="H331" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" s="16" t="s">
+        <v>697</v>
+      </c>
+      <c r="B332" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C332" s="17" t="s">
+        <v>698</v>
+      </c>
+      <c r="D332" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E332" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F332" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G332" s="19">
+        <v>40</v>
+      </c>
+      <c r="H332" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="B333" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C333" s="17" t="s">
+        <v>700</v>
+      </c>
+      <c r="D333" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E333" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F333" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G333" s="19">
+        <v>30</v>
+      </c>
+      <c r="H333" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="B334" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C334" s="17" t="s">
+        <v>702</v>
+      </c>
+      <c r="D334" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E334" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F334" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G334" s="19">
+        <v>47</v>
+      </c>
+      <c r="H334" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" s="16" t="s">
+        <v>703</v>
+      </c>
+      <c r="B335" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C335" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="D335" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E335" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F335" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G335" s="19">
+        <v>27</v>
+      </c>
+      <c r="H335" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" s="16" t="s">
+        <v>705</v>
+      </c>
+      <c r="B336" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C336" s="17" t="s">
+        <v>706</v>
+      </c>
+      <c r="D336" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E336" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F336" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G336" s="19">
+        <v>3</v>
+      </c>
+      <c r="H336" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A337" s="16" t="s">
+        <v>707</v>
+      </c>
+      <c r="B337" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C337" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="D337" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E337" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F337" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G337" s="19">
+        <v>7</v>
+      </c>
+      <c r="H337" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A338" s="16" t="s">
+        <v>709</v>
+      </c>
+      <c r="B338" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C338" s="17" t="s">
+        <v>710</v>
+      </c>
+      <c r="D338" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E338" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F338" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G338" s="19">
+        <v>22</v>
+      </c>
+      <c r="H338" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A339" s="16" t="s">
+        <v>711</v>
+      </c>
+      <c r="B339" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C339" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="D339" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E339" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F339" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G339" s="19">
+        <v>6</v>
+      </c>
+      <c r="H339" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A340" s="16" t="s">
+        <v>713</v>
+      </c>
+      <c r="B340" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C340" s="17" t="s">
+        <v>714</v>
+      </c>
+      <c r="D340" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E340" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F340" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G340" s="19">
+        <v>41</v>
+      </c>
+      <c r="H340" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A341" s="16" t="s">
+        <v>715</v>
+      </c>
+      <c r="B341" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C341" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="D341" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E341" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F341" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G341" s="19">
+        <v>42</v>
+      </c>
+      <c r="H341" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A342" s="16" t="s">
+        <v>717</v>
+      </c>
+      <c r="B342" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C342" s="17" t="s">
+        <v>718</v>
+      </c>
+      <c r="D342" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E342" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F342" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G342" s="19">
+        <v>33</v>
+      </c>
+      <c r="H342" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A343" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="B343" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C343" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="D343" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E343" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F343" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G343" s="19">
+        <v>3</v>
+      </c>
+      <c r="H343" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A344" s="16" t="s">
+        <v>721</v>
+      </c>
+      <c r="B344" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C344" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="D344" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E344" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F344" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G344" s="19">
+        <v>27</v>
+      </c>
+      <c r="H344" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A345" s="16" t="s">
+        <v>723</v>
+      </c>
+      <c r="B345" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C345" s="17" t="s">
+        <v>724</v>
+      </c>
+      <c r="D345" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E345" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F345" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G345" s="19">
+        <v>27</v>
+      </c>
+      <c r="H345" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A346" s="16" t="s">
+        <v>725</v>
+      </c>
+      <c r="B346" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C346" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="D346" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E346" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F346" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G346" s="19">
+        <v>34</v>
+      </c>
+      <c r="H346" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A347" s="16" t="s">
+        <v>727</v>
+      </c>
+      <c r="B347" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C347" s="17" t="s">
+        <v>728</v>
+      </c>
+      <c r="D347" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E347" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F347" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G347" s="19">
+        <v>44</v>
+      </c>
+      <c r="H347" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A348" s="16" t="s">
+        <v>729</v>
+      </c>
+      <c r="B348" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C348" s="17" t="s">
+        <v>730</v>
+      </c>
+      <c r="D348" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E348" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F348" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G348" s="19">
+        <v>45</v>
+      </c>
+      <c r="H348" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A349" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="B349" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C349" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="D349" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E349" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F349" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G349" s="19">
+        <v>2</v>
+      </c>
+      <c r="H349" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A350" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="B350" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C350" s="17" t="s">
+        <v>734</v>
+      </c>
+      <c r="D350" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E350" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F350" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G350" s="19">
+        <v>49</v>
+      </c>
+      <c r="H350" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A351" s="16" t="s">
+        <v>735</v>
+      </c>
+      <c r="B351" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C351" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="D351" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E351" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F351" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G351" s="19">
+        <v>25</v>
+      </c>
+      <c r="H351" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A352" s="16" t="s">
+        <v>737</v>
+      </c>
+      <c r="B352" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C352" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="D352" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E352" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F352" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G352" s="19">
+        <v>29</v>
+      </c>
+      <c r="H352" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="16" t="s">
+        <v>739</v>
+      </c>
+      <c r="B353" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C353" s="17" t="s">
+        <v>740</v>
+      </c>
+      <c r="D353" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E353" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F353" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G353" s="19">
+        <v>11</v>
+      </c>
+      <c r="H353" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A354" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="B354" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C354" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="D354" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E354" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F354" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G354" s="19">
+        <v>41</v>
+      </c>
+      <c r="H354" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" s="16" t="s">
+        <v>743</v>
+      </c>
+      <c r="B355" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C355" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="D355" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E355" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F355" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G355" s="19">
+        <v>2</v>
+      </c>
+      <c r="H355" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="16" t="s">
+        <v>745</v>
+      </c>
+      <c r="B356" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C356" s="17" t="s">
+        <v>746</v>
+      </c>
+      <c r="D356" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E356" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F356" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G356" s="19">
+        <v>12</v>
+      </c>
+      <c r="H356" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357" s="16" t="s">
+        <v>747</v>
+      </c>
+      <c r="B357" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C357" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="D357" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E357" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F357" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G357" s="19">
+        <v>40</v>
+      </c>
+      <c r="H357" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358" s="16" t="s">
+        <v>749</v>
+      </c>
+      <c r="B358" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C358" s="17" t="s">
+        <v>750</v>
+      </c>
+      <c r="D358" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E358" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F358" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G358" s="19">
+        <v>18</v>
+      </c>
+      <c r="H358" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="B359" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C359" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="D359" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E359" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F359" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G359" s="19">
+        <v>42</v>
+      </c>
+      <c r="H359" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="16" t="s">
+        <v>753</v>
+      </c>
+      <c r="B360" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C360" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="D360" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E360" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F360" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G360" s="19">
+        <v>17</v>
+      </c>
+      <c r="H360" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="B361" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C361" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="D361" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E361" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F361" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G361" s="19">
+        <v>29</v>
+      </c>
+      <c r="H361" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="B362" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C362" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="D362" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E362" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F362" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G362" s="19">
+        <v>37</v>
+      </c>
+      <c r="H362" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="B363" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C363" s="17" t="s">
+        <v>760</v>
+      </c>
+      <c r="D363" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E363" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F363" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G363" s="19">
+        <v>24</v>
+      </c>
+      <c r="H363" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" s="16" t="s">
+        <v>761</v>
+      </c>
+      <c r="B364" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C364" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="D364" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E364" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F364" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G364" s="19">
+        <v>17</v>
+      </c>
+      <c r="H364" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="B365" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C365" s="17" t="s">
+        <v>764</v>
+      </c>
+      <c r="D365" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E365" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F365" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G365" s="19">
+        <v>1</v>
+      </c>
+      <c r="H365" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" s="16" t="s">
+        <v>765</v>
+      </c>
+      <c r="B366" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C366" s="17" t="s">
+        <v>766</v>
+      </c>
+      <c r="D366" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E366" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F366" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G366" s="19">
+        <v>36</v>
+      </c>
+      <c r="H366" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" s="16" t="s">
+        <v>767</v>
+      </c>
+      <c r="B367" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C367" s="17" t="s">
+        <v>768</v>
+      </c>
+      <c r="D367" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E367" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F367" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G367" s="19">
+        <v>23</v>
+      </c>
+      <c r="H367" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="B368" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C368" s="17" t="s">
+        <v>770</v>
+      </c>
+      <c r="D368" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E368" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F368" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G368" s="19">
+        <v>37</v>
+      </c>
+      <c r="H368" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A369" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="B369" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C369" s="17" t="s">
+        <v>772</v>
+      </c>
+      <c r="D369" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E369" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F369" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G369" s="19">
+        <v>0</v>
+      </c>
+      <c r="H369" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A370" s="16" t="s">
+        <v>773</v>
+      </c>
+      <c r="B370" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C370" s="17" t="s">
+        <v>774</v>
+      </c>
+      <c r="D370" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E370" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F370" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G370" s="19">
+        <v>3</v>
+      </c>
+      <c r="H370" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A371" s="16" t="s">
+        <v>775</v>
+      </c>
+      <c r="B371" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C371" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="D371" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E371" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F371" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G371" s="19">
+        <v>19</v>
+      </c>
+      <c r="H371" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A372" s="16" t="s">
+        <v>777</v>
+      </c>
+      <c r="B372" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C372" s="17" t="s">
+        <v>778</v>
+      </c>
+      <c r="D372" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E372" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F372" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G372" s="19">
+        <v>0</v>
+      </c>
+      <c r="H372" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A373" s="16" t="s">
+        <v>779</v>
+      </c>
+      <c r="B373" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C373" s="17" t="s">
+        <v>780</v>
+      </c>
+      <c r="D373" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E373" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F373" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G373" s="19">
+        <v>4</v>
+      </c>
+      <c r="H373" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A374" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="B374" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C374" s="17" t="s">
+        <v>782</v>
+      </c>
+      <c r="D374" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E374" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F374" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G374" s="19">
+        <v>9</v>
+      </c>
+      <c r="H374" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A375" s="16" t="s">
+        <v>783</v>
+      </c>
+      <c r="B375" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C375" s="17" t="s">
+        <v>784</v>
+      </c>
+      <c r="D375" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E375" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F375" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G375" s="19">
+        <v>34</v>
+      </c>
+      <c r="H375" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A376" s="16" t="s">
+        <v>785</v>
+      </c>
+      <c r="B376" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C376" s="17" t="s">
+        <v>786</v>
+      </c>
+      <c r="D376" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E376" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F376" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G376" s="19">
+        <v>10</v>
+      </c>
+      <c r="H376" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A377" s="16" t="s">
+        <v>787</v>
+      </c>
+      <c r="B377" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C377" s="17" t="s">
+        <v>788</v>
+      </c>
+      <c r="D377" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E377" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F377" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G377" s="19">
+        <v>2</v>
+      </c>
+      <c r="H377" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A378" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="B378" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C378" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="D378" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E378" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F378" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G378" s="19">
+        <v>45</v>
+      </c>
+      <c r="H378" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A379" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="B379" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C379" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="D379" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E379" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F379" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G379" s="19">
+        <v>10</v>
+      </c>
+      <c r="H379" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A380" s="16" t="s">
+        <v>793</v>
+      </c>
+      <c r="B380" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C380" s="17" t="s">
+        <v>794</v>
+      </c>
+      <c r="D380" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E380" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F380" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G380" s="19">
+        <v>3</v>
+      </c>
+      <c r="H380" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A381" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="B381" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C381" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="D381" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E381" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F381" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G381" s="19">
+        <v>39</v>
+      </c>
+      <c r="H381" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A382" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="B382" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C382" s="17" t="s">
+        <v>798</v>
+      </c>
+      <c r="D382" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E382" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F382" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G382" s="19">
+        <v>20</v>
+      </c>
+      <c r="H382" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A383" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="B383" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C383" s="17" t="s">
+        <v>800</v>
+      </c>
+      <c r="D383" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E383" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F383" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G383" s="19">
+        <v>35</v>
+      </c>
+      <c r="H383" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A384" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="B384" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C384" s="17" t="s">
+        <v>802</v>
+      </c>
+      <c r="D384" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E384" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F384" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G384" s="19">
+        <v>14</v>
+      </c>
+      <c r="H384" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A385" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="B385" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C385" s="17" t="s">
+        <v>804</v>
+      </c>
+      <c r="D385" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E385" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F385" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G385" s="19">
+        <v>11</v>
+      </c>
+      <c r="H385" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A386" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="B386" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C386" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="D386" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E386" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F386" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G386" s="19">
+        <v>25</v>
+      </c>
+      <c r="H386" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A387" s="16" t="s">
+        <v>807</v>
+      </c>
+      <c r="B387" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C387" s="17" t="s">
+        <v>808</v>
+      </c>
+      <c r="D387" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E387" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F387" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G387" s="19">
+        <v>5</v>
+      </c>
+      <c r="H387" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A388" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="B388" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C388" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="D388" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E388" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F388" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G388" s="19">
+        <v>16</v>
+      </c>
+      <c r="H388" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A389" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="B389" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C389" s="17" t="s">
+        <v>812</v>
+      </c>
+      <c r="D389" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E389" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F389" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G389" s="19">
+        <v>43</v>
+      </c>
+      <c r="H389" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A390" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="B390" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C390" s="17" t="s">
+        <v>814</v>
+      </c>
+      <c r="D390" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E390" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F390" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G390" s="19">
+        <v>39</v>
+      </c>
+      <c r="H390" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A391" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="B391" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C391" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="D391" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E391" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F391" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G391" s="19">
+        <v>2</v>
+      </c>
+      <c r="H391" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A392" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="B392" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C392" s="17" t="s">
+        <v>818</v>
+      </c>
+      <c r="D392" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E392" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F392" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G392" s="19">
+        <v>30</v>
+      </c>
+      <c r="H392" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A393" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="B393" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C393" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="D393" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E393" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F393" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G393" s="19">
+        <v>5</v>
+      </c>
+      <c r="H393" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A394" s="16" t="s">
+        <v>821</v>
+      </c>
+      <c r="B394" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C394" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="D394" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E394" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F394" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G394" s="19">
+        <v>13</v>
+      </c>
+      <c r="H394" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A395" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="B395" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C395" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="D395" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E395" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F395" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G395" s="19">
+        <v>31</v>
+      </c>
+      <c r="H395" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A396" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="B396" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C396" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="D396" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E396" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F396" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G396" s="19">
+        <v>24</v>
+      </c>
+      <c r="H396" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A397" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="B397" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C397" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="D397" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E397" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F397" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G397" s="19">
+        <v>6</v>
+      </c>
+      <c r="H397" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A398" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="B398" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C398" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="D398" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E398" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F398" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G398" s="19">
+        <v>34</v>
+      </c>
+      <c r="H398" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A399" s="16" t="s">
+        <v>831</v>
+      </c>
+      <c r="B399" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C399" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="D399" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E399" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F399" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G399" s="19">
+        <v>20</v>
+      </c>
+      <c r="H399" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A400" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="B400" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C400" s="17" t="s">
+        <v>834</v>
+      </c>
+      <c r="D400" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E400" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F400" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G400" s="19">
+        <v>26</v>
+      </c>
+      <c r="H400" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A401" s="16" t="s">
+        <v>835</v>
+      </c>
+      <c r="B401" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C401" s="17" t="s">
+        <v>836</v>
+      </c>
+      <c r="D401" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E401" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F401" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G401" s="19">
+        <v>19</v>
+      </c>
+      <c r="H401" s="17" t="s">
         <v>37</v>
       </c>
     </row>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>6/23/2026, 10:07:08 AM</t>
+    <t>6/23/2026, 11:04:16 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>13.32 seconds</t>
+    <t>14.81 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>6/23/2026, 11:04:16 AM</t>
+    <t>6/23/2026, 11:27:38 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>14.81 seconds</t>
+    <t>7.04 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>6/23/2026, 11:27:38 AM</t>
+    <t>7/19/2026, 3:50:51 PM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>7.04 seconds</t>
+    <t>16.11 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/19/2026, 3:50:51 PM</t>
+    <t>7/19/2026, 4:36:24 PM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>16.11 seconds</t>
+    <t>7.84 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/19/2026, 4:36:24 PM</t>
+    <t>7/19/2026, 4:51:48 PM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>7.84 seconds</t>
+    <t>7.57 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/19/2026, 4:51:48 PM</t>
+    <t>7/19/2026, 5:50:18 PM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>7.57 seconds</t>
+    <t>15.63 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/19/2026, 5:50:18 PM</t>
+    <t>7/19/2026, 6:07:43 PM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>15.63 seconds</t>
+    <t>7.98 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/19/2026, 6:07:43 PM</t>
+    <t>7/22/2026, 5:52:01 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>7.98 seconds</t>
+    <t>16.59 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 5:52:01 AM</t>
+    <t>7/22/2026, 6:09:32 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>16.59 seconds</t>
+    <t>14.89 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 6:09:32 AM</t>
+    <t>7/22/2026, 6:26:34 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>14.89 seconds</t>
+    <t>15.71 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 6:26:34 AM</t>
+    <t>7/22/2026, 6:45:02 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>15.71 seconds</t>
+    <t>12.87 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 6:45:02 AM</t>
+    <t>7/22/2026, 7:03:20 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>12.87 seconds</t>
+    <t>13.87 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 7:03:20 AM</t>
+    <t>7/22/2026, 7:27:53 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>13.87 seconds</t>
+    <t>7.45 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 7:27:53 AM</t>
+    <t>7/22/2026, 7:45:21 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>7.45 seconds</t>
+    <t>15.47 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 7:45:21 AM</t>
+    <t>7/22/2026, 8:04:10 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>15.47 seconds</t>
+    <t>17.05 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 8:04:10 AM</t>
+    <t>7/22/2026, 8:15:47 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>17.05 seconds</t>
+    <t>14.16 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 8:15:47 AM</t>
+    <t>7/22/2026, 8:34:02 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>14.16 seconds</t>
+    <t>17.99 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 8:34:02 AM</t>
+    <t>7/22/2026, 8:49:45 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>17.99 seconds</t>
+    <t>8.16 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 8:49:45 AM</t>
+    <t>7/22/2026, 9:09:15 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>8.16 seconds</t>
+    <t>12.27 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 9:09:15 AM</t>
+    <t>7/22/2026, 9:27:58 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>12.27 seconds</t>
+    <t>11.35 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 9:27:58 AM</t>
+    <t>7/22/2026, 9:45:24 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>11.35 seconds</t>
+    <t>8.02 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 9:45:24 AM</t>
+    <t>7/22/2026, 10:03:45 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>8.02 seconds</t>
+    <t>15.07 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 10:03:45 AM</t>
+    <t>7/22/2026, 10:25:40 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>15.07 seconds</t>
+    <t>13.59 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 10:25:40 AM</t>
+    <t>7/22/2026, 10:44:57 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>13.59 seconds</t>
+    <t>16.04 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7039,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="G143" s="19">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H143" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8339,7 +8339,7 @@
         <v>36</v>
       </c>
       <c r="G193" s="19">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H193" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8859,7 +8859,7 @@
         <v>36</v>
       </c>
       <c r="G213" s="19">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H213" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10679,7 +10679,7 @@
         <v>36</v>
       </c>
       <c r="G283" s="19">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H283" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11121,7 +11121,7 @@
         <v>36</v>
       </c>
       <c r="G300" s="19">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H300" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13487,7 +13487,7 @@
         <v>36</v>
       </c>
       <c r="G391" s="19">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H391" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13565,7 +13565,7 @@
         <v>36</v>
       </c>
       <c r="G394" s="19">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H394" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 10:44:57 AM</t>
+    <t>7/22/2026, 10:59:15 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>16.04 seconds</t>
+    <t>14.09 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4127,7 +4127,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="19">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4595,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H49" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v>
       </c>
       <c r="G61" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H61" s="17" t="s">
         <v>37</v>
@@ -4933,7 +4933,7 @@
         <v>36</v>
       </c>
       <c r="G62" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H62" s="17" t="s">
         <v>37</v>
@@ -4959,7 +4959,7 @@
         <v>36</v>
       </c>
       <c r="G63" s="19">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>37</v>
@@ -4985,7 +4985,7 @@
         <v>36</v>
       </c>
       <c r="G64" s="19">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H64" s="17" t="s">
         <v>37</v>
@@ -5011,7 +5011,7 @@
         <v>36</v>
       </c>
       <c r="G65" s="19">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H65" s="17" t="s">
         <v>37</v>
@@ -5037,7 +5037,7 @@
         <v>36</v>
       </c>
       <c r="G66" s="19">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H66" s="17" t="s">
         <v>37</v>
@@ -5063,7 +5063,7 @@
         <v>36</v>
       </c>
       <c r="G67" s="19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H67" s="17" t="s">
         <v>37</v>
@@ -5089,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="G68" s="19">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="H68" s="17" t="s">
         <v>37</v>
@@ -5115,7 +5115,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="19">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H69" s="17" t="s">
         <v>37</v>
@@ -5141,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="G70" s="19">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H70" s="17" t="s">
         <v>37</v>
@@ -5167,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="G71" s="19">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="H71" s="17" t="s">
         <v>37</v>
@@ -5193,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="G72" s="19">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H72" s="17" t="s">
         <v>37</v>
@@ -5219,7 +5219,7 @@
         <v>36</v>
       </c>
       <c r="G73" s="19">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H73" s="17" t="s">
         <v>37</v>
@@ -5245,7 +5245,7 @@
         <v>36</v>
       </c>
       <c r="G74" s="19">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H74" s="17" t="s">
         <v>37</v>
@@ -5271,7 +5271,7 @@
         <v>36</v>
       </c>
       <c r="G75" s="19">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H75" s="17" t="s">
         <v>37</v>
@@ -5297,7 +5297,7 @@
         <v>36</v>
       </c>
       <c r="G76" s="19">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H76" s="17" t="s">
         <v>37</v>
@@ -5323,7 +5323,7 @@
         <v>36</v>
       </c>
       <c r="G77" s="19">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H77" s="17" t="s">
         <v>37</v>
@@ -5349,7 +5349,7 @@
         <v>36</v>
       </c>
       <c r="G78" s="19">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H78" s="17" t="s">
         <v>37</v>
@@ -5375,7 +5375,7 @@
         <v>36</v>
       </c>
       <c r="G79" s="19">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H79" s="17" t="s">
         <v>37</v>
@@ -5401,7 +5401,7 @@
         <v>36</v>
       </c>
       <c r="G80" s="19">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H80" s="17" t="s">
         <v>37</v>
@@ -5427,7 +5427,7 @@
         <v>36</v>
       </c>
       <c r="G81" s="19">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H81" s="17" t="s">
         <v>37</v>
@@ -5453,7 +5453,7 @@
         <v>36</v>
       </c>
       <c r="G82" s="19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H82" s="17" t="s">
         <v>37</v>
@@ -5479,7 +5479,7 @@
         <v>36</v>
       </c>
       <c r="G83" s="19">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="H83" s="17" t="s">
         <v>37</v>
@@ -5505,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="G84" s="19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H84" s="17" t="s">
         <v>37</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G85" s="19">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>37</v>
@@ -5557,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="G86" s="19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>37</v>
@@ -5583,7 +5583,7 @@
         <v>36</v>
       </c>
       <c r="G87" s="19">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>37</v>
@@ -5609,7 +5609,7 @@
         <v>36</v>
       </c>
       <c r="G88" s="19">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>37</v>
@@ -5635,7 +5635,7 @@
         <v>36</v>
       </c>
       <c r="G89" s="19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>37</v>
@@ -5661,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="G90" s="19">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="H90" s="17" t="s">
         <v>37</v>
@@ -5687,7 +5687,7 @@
         <v>36</v>
       </c>
       <c r="G91" s="19">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>37</v>
@@ -5713,7 +5713,7 @@
         <v>36</v>
       </c>
       <c r="G92" s="19">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H92" s="17" t="s">
         <v>37</v>
@@ -5739,7 +5739,7 @@
         <v>36</v>
       </c>
       <c r="G93" s="19">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H93" s="17" t="s">
         <v>37</v>
@@ -5765,7 +5765,7 @@
         <v>36</v>
       </c>
       <c r="G94" s="19">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H94" s="17" t="s">
         <v>37</v>
@@ -5791,7 +5791,7 @@
         <v>36</v>
       </c>
       <c r="G95" s="19">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>37</v>
@@ -5817,7 +5817,7 @@
         <v>36</v>
       </c>
       <c r="G96" s="19">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H96" s="17" t="s">
         <v>37</v>
@@ -5843,7 +5843,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H97" s="17" t="s">
         <v>37</v>
@@ -5869,7 +5869,7 @@
         <v>36</v>
       </c>
       <c r="G98" s="19">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>37</v>
@@ -5895,7 +5895,7 @@
         <v>36</v>
       </c>
       <c r="G99" s="19">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H99" s="17" t="s">
         <v>37</v>
@@ -5921,7 +5921,7 @@
         <v>36</v>
       </c>
       <c r="G100" s="19">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H100" s="17" t="s">
         <v>37</v>
@@ -5947,7 +5947,7 @@
         <v>36</v>
       </c>
       <c r="G101" s="19">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H101" s="17" t="s">
         <v>37</v>
@@ -5973,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="G102" s="19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H102" s="17" t="s">
         <v>37</v>
@@ -5999,7 +5999,7 @@
         <v>36</v>
       </c>
       <c r="G103" s="19">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H103" s="17" t="s">
         <v>37</v>
@@ -6025,7 +6025,7 @@
         <v>36</v>
       </c>
       <c r="G104" s="19">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="H104" s="17" t="s">
         <v>37</v>
@@ -6051,7 +6051,7 @@
         <v>36</v>
       </c>
       <c r="G105" s="19">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H105" s="17" t="s">
         <v>37</v>
@@ -6077,7 +6077,7 @@
         <v>36</v>
       </c>
       <c r="G106" s="19">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>37</v>
@@ -6103,7 +6103,7 @@
         <v>36</v>
       </c>
       <c r="G107" s="19">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H107" s="17" t="s">
         <v>37</v>
@@ -6129,7 +6129,7 @@
         <v>36</v>
       </c>
       <c r="G108" s="19">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>37</v>
@@ -6155,7 +6155,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>37</v>
@@ -6181,7 +6181,7 @@
         <v>36</v>
       </c>
       <c r="G110" s="19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H110" s="17" t="s">
         <v>37</v>
@@ -6207,7 +6207,7 @@
         <v>36</v>
       </c>
       <c r="G111" s="19">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H111" s="17" t="s">
         <v>37</v>
@@ -6233,7 +6233,7 @@
         <v>36</v>
       </c>
       <c r="G112" s="19">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H112" s="17" t="s">
         <v>37</v>
@@ -6259,7 +6259,7 @@
         <v>36</v>
       </c>
       <c r="G113" s="19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H113" s="17" t="s">
         <v>37</v>
@@ -6285,7 +6285,7 @@
         <v>36</v>
       </c>
       <c r="G114" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H114" s="17" t="s">
         <v>37</v>
@@ -6311,7 +6311,7 @@
         <v>36</v>
       </c>
       <c r="G115" s="19">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H115" s="17" t="s">
         <v>37</v>
@@ -6337,7 +6337,7 @@
         <v>36</v>
       </c>
       <c r="G116" s="19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H116" s="17" t="s">
         <v>37</v>
@@ -6363,7 +6363,7 @@
         <v>36</v>
       </c>
       <c r="G117" s="19">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H117" s="17" t="s">
         <v>37</v>
@@ -6389,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="G118" s="19">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H118" s="17" t="s">
         <v>37</v>
@@ -6415,7 +6415,7 @@
         <v>36</v>
       </c>
       <c r="G119" s="19">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>37</v>
@@ -6441,7 +6441,7 @@
         <v>36</v>
       </c>
       <c r="G120" s="19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>37</v>
@@ -6467,7 +6467,7 @@
         <v>36</v>
       </c>
       <c r="G121" s="19">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H121" s="17" t="s">
         <v>37</v>
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="19">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H122" s="17" t="s">
         <v>37</v>
@@ -6519,7 +6519,7 @@
         <v>36</v>
       </c>
       <c r="G123" s="19">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H123" s="17" t="s">
         <v>37</v>
@@ -6545,7 +6545,7 @@
         <v>36</v>
       </c>
       <c r="G124" s="19">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H124" s="17" t="s">
         <v>37</v>
@@ -6571,7 +6571,7 @@
         <v>36</v>
       </c>
       <c r="G125" s="19">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H125" s="17" t="s">
         <v>37</v>
@@ -6597,7 +6597,7 @@
         <v>36</v>
       </c>
       <c r="G126" s="19">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H126" s="17" t="s">
         <v>37</v>
@@ -6623,7 +6623,7 @@
         <v>36</v>
       </c>
       <c r="G127" s="19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H127" s="17" t="s">
         <v>37</v>
@@ -6649,7 +6649,7 @@
         <v>36</v>
       </c>
       <c r="G128" s="19">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H128" s="17" t="s">
         <v>37</v>
@@ -6675,7 +6675,7 @@
         <v>36</v>
       </c>
       <c r="G129" s="19">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H129" s="17" t="s">
         <v>37</v>
@@ -6701,7 +6701,7 @@
         <v>36</v>
       </c>
       <c r="G130" s="19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H130" s="17" t="s">
         <v>37</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="G131" s="19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H131" s="17" t="s">
         <v>37</v>
@@ -6753,7 +6753,7 @@
         <v>36</v>
       </c>
       <c r="G132" s="19">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H132" s="17" t="s">
         <v>37</v>
@@ -6779,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="G133" s="19">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H133" s="17" t="s">
         <v>37</v>
@@ -6805,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="G134" s="19">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H134" s="17" t="s">
         <v>37</v>
@@ -6831,7 +6831,7 @@
         <v>36</v>
       </c>
       <c r="G135" s="19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H135" s="17" t="s">
         <v>37</v>
@@ -6857,7 +6857,7 @@
         <v>36</v>
       </c>
       <c r="G136" s="19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H136" s="17" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="G137" s="19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H137" s="17" t="s">
         <v>37</v>
@@ -6909,7 +6909,7 @@
         <v>36</v>
       </c>
       <c r="G138" s="19">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="H138" s="17" t="s">
         <v>37</v>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
       <c r="G139" s="19">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H139" s="17" t="s">
         <v>37</v>
@@ -6961,7 +6961,7 @@
         <v>36</v>
       </c>
       <c r="G140" s="19">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H140" s="17" t="s">
         <v>37</v>
@@ -6987,7 +6987,7 @@
         <v>36</v>
       </c>
       <c r="G141" s="19">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H141" s="17" t="s">
         <v>37</v>
@@ -7013,7 +7013,7 @@
         <v>36</v>
       </c>
       <c r="G142" s="19">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="H142" s="17" t="s">
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>36</v>
       </c>
       <c r="G144" s="19">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H144" s="17" t="s">
         <v>37</v>
@@ -7091,7 +7091,7 @@
         <v>36</v>
       </c>
       <c r="G145" s="19">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H145" s="17" t="s">
         <v>37</v>
@@ -7117,7 +7117,7 @@
         <v>36</v>
       </c>
       <c r="G146" s="19">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H146" s="17" t="s">
         <v>37</v>
@@ -7143,7 +7143,7 @@
         <v>36</v>
       </c>
       <c r="G147" s="19">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H147" s="17" t="s">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>36</v>
       </c>
       <c r="G148" s="19">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H148" s="17" t="s">
         <v>37</v>
@@ -7195,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="G149" s="19">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H149" s="17" t="s">
         <v>37</v>
@@ -7221,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="G150" s="19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H150" s="17" t="s">
         <v>37</v>
@@ -7247,7 +7247,7 @@
         <v>36</v>
       </c>
       <c r="G151" s="19">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H151" s="17" t="s">
         <v>37</v>
@@ -7273,7 +7273,7 @@
         <v>36</v>
       </c>
       <c r="G152" s="19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H152" s="17" t="s">
         <v>37</v>
@@ -7299,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="G153" s="19">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H153" s="17" t="s">
         <v>37</v>
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="G154" s="19">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H154" s="17" t="s">
         <v>37</v>
@@ -7351,7 +7351,7 @@
         <v>36</v>
       </c>
       <c r="G155" s="19">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H155" s="17" t="s">
         <v>37</v>
@@ -7377,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="G156" s="19">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H156" s="17" t="s">
         <v>37</v>
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="G157" s="19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H157" s="17" t="s">
         <v>37</v>
@@ -7429,7 +7429,7 @@
         <v>36</v>
       </c>
       <c r="G158" s="19">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H158" s="17" t="s">
         <v>37</v>
@@ -7455,7 +7455,7 @@
         <v>36</v>
       </c>
       <c r="G159" s="19">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H159" s="17" t="s">
         <v>37</v>
@@ -7481,7 +7481,7 @@
         <v>36</v>
       </c>
       <c r="G160" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H160" s="17" t="s">
         <v>37</v>
@@ -7507,7 +7507,7 @@
         <v>36</v>
       </c>
       <c r="G161" s="19">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H161" s="17" t="s">
         <v>37</v>
@@ -7533,7 +7533,7 @@
         <v>36</v>
       </c>
       <c r="G162" s="19">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H162" s="17" t="s">
         <v>37</v>
@@ -7559,7 +7559,7 @@
         <v>36</v>
       </c>
       <c r="G163" s="19">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H163" s="17" t="s">
         <v>37</v>
@@ -7585,7 +7585,7 @@
         <v>36</v>
       </c>
       <c r="G164" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H164" s="17" t="s">
         <v>37</v>
@@ -7611,7 +7611,7 @@
         <v>36</v>
       </c>
       <c r="G165" s="19">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H165" s="17" t="s">
         <v>37</v>
@@ -7637,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="G166" s="19">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H166" s="17" t="s">
         <v>37</v>
@@ -7663,7 +7663,7 @@
         <v>36</v>
       </c>
       <c r="G167" s="19">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="H167" s="17" t="s">
         <v>37</v>
@@ -7689,7 +7689,7 @@
         <v>36</v>
       </c>
       <c r="G168" s="19">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H168" s="17" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>36</v>
       </c>
       <c r="G169" s="19">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H169" s="17" t="s">
         <v>37</v>
@@ -7741,7 +7741,7 @@
         <v>36</v>
       </c>
       <c r="G170" s="19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H170" s="17" t="s">
         <v>37</v>
@@ -7767,7 +7767,7 @@
         <v>36</v>
       </c>
       <c r="G171" s="19">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H171" s="17" t="s">
         <v>37</v>
@@ -7793,7 +7793,7 @@
         <v>36</v>
       </c>
       <c r="G172" s="19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H172" s="17" t="s">
         <v>37</v>
@@ -7819,7 +7819,7 @@
         <v>36</v>
       </c>
       <c r="G173" s="19">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H173" s="17" t="s">
         <v>37</v>
@@ -7845,7 +7845,7 @@
         <v>36</v>
       </c>
       <c r="G174" s="19">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H174" s="17" t="s">
         <v>37</v>
@@ -7871,7 +7871,7 @@
         <v>36</v>
       </c>
       <c r="G175" s="19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H175" s="17" t="s">
         <v>37</v>
@@ -7897,7 +7897,7 @@
         <v>36</v>
       </c>
       <c r="G176" s="19">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H176" s="17" t="s">
         <v>37</v>
@@ -7923,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="G177" s="19">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H177" s="17" t="s">
         <v>37</v>
@@ -7949,7 +7949,7 @@
         <v>36</v>
       </c>
       <c r="G178" s="19">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H178" s="17" t="s">
         <v>37</v>
@@ -7975,7 +7975,7 @@
         <v>36</v>
       </c>
       <c r="G179" s="19">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H179" s="17" t="s">
         <v>37</v>
@@ -8001,7 +8001,7 @@
         <v>36</v>
       </c>
       <c r="G180" s="19">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="H180" s="17" t="s">
         <v>37</v>
@@ -8027,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="G181" s="19">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H181" s="17" t="s">
         <v>37</v>
@@ -8053,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="G182" s="19">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="H182" s="17" t="s">
         <v>37</v>
@@ -8079,7 +8079,7 @@
         <v>36</v>
       </c>
       <c r="G183" s="19">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H183" s="17" t="s">
         <v>37</v>
@@ -8105,7 +8105,7 @@
         <v>36</v>
       </c>
       <c r="G184" s="19">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H184" s="17" t="s">
         <v>37</v>
@@ -8131,7 +8131,7 @@
         <v>36</v>
       </c>
       <c r="G185" s="19">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H185" s="17" t="s">
         <v>37</v>
@@ -8157,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="G186" s="19">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H186" s="17" t="s">
         <v>37</v>
@@ -8183,7 +8183,7 @@
         <v>36</v>
       </c>
       <c r="G187" s="19">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H187" s="17" t="s">
         <v>37</v>
@@ -8209,7 +8209,7 @@
         <v>36</v>
       </c>
       <c r="G188" s="19">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H188" s="17" t="s">
         <v>37</v>
@@ -8235,7 +8235,7 @@
         <v>36</v>
       </c>
       <c r="G189" s="19">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="H189" s="17" t="s">
         <v>37</v>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="G190" s="19">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H190" s="17" t="s">
         <v>37</v>
@@ -8287,7 +8287,7 @@
         <v>36</v>
       </c>
       <c r="G191" s="19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H191" s="17" t="s">
         <v>37</v>
@@ -8313,7 +8313,7 @@
         <v>36</v>
       </c>
       <c r="G192" s="19">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H192" s="17" t="s">
         <v>37</v>
@@ -8365,7 +8365,7 @@
         <v>36</v>
       </c>
       <c r="G194" s="19">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H194" s="17" t="s">
         <v>37</v>
@@ -8391,7 +8391,7 @@
         <v>36</v>
       </c>
       <c r="G195" s="19">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H195" s="17" t="s">
         <v>37</v>
@@ -8417,7 +8417,7 @@
         <v>36</v>
       </c>
       <c r="G196" s="19">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H196" s="17" t="s">
         <v>37</v>
@@ -8443,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="G197" s="19">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H197" s="17" t="s">
         <v>37</v>
@@ -8469,7 +8469,7 @@
         <v>36</v>
       </c>
       <c r="G198" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H198" s="17" t="s">
         <v>37</v>
@@ -8495,7 +8495,7 @@
         <v>36</v>
       </c>
       <c r="G199" s="19">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H199" s="17" t="s">
         <v>37</v>
@@ -8521,7 +8521,7 @@
         <v>36</v>
       </c>
       <c r="G200" s="19">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H200" s="17" t="s">
         <v>37</v>
@@ -8547,7 +8547,7 @@
         <v>36</v>
       </c>
       <c r="G201" s="19">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H201" s="17" t="s">
         <v>37</v>
@@ -8573,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="G202" s="19">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H202" s="17" t="s">
         <v>37</v>
@@ -8599,7 +8599,7 @@
         <v>36</v>
       </c>
       <c r="G203" s="19">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H203" s="17" t="s">
         <v>37</v>
@@ -8625,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="G204" s="19">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H204" s="17" t="s">
         <v>37</v>
@@ -8651,7 +8651,7 @@
         <v>36</v>
       </c>
       <c r="G205" s="19">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="H205" s="17" t="s">
         <v>37</v>
@@ -8677,7 +8677,7 @@
         <v>36</v>
       </c>
       <c r="G206" s="19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H206" s="17" t="s">
         <v>37</v>
@@ -8703,7 +8703,7 @@
         <v>36</v>
       </c>
       <c r="G207" s="19">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H207" s="17" t="s">
         <v>37</v>
@@ -8729,7 +8729,7 @@
         <v>36</v>
       </c>
       <c r="G208" s="19">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H208" s="17" t="s">
         <v>37</v>
@@ -8755,7 +8755,7 @@
         <v>36</v>
       </c>
       <c r="G209" s="19">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H209" s="17" t="s">
         <v>37</v>
@@ -8781,7 +8781,7 @@
         <v>36</v>
       </c>
       <c r="G210" s="19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H210" s="17" t="s">
         <v>37</v>
@@ -8807,7 +8807,7 @@
         <v>36</v>
       </c>
       <c r="G211" s="19">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H211" s="17" t="s">
         <v>37</v>
@@ -8833,7 +8833,7 @@
         <v>36</v>
       </c>
       <c r="G212" s="19">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H212" s="17" t="s">
         <v>37</v>
@@ -8885,7 +8885,7 @@
         <v>36</v>
       </c>
       <c r="G214" s="19">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H214" s="17" t="s">
         <v>37</v>
@@ -8911,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="G215" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H215" s="17" t="s">
         <v>37</v>
@@ -8937,7 +8937,7 @@
         <v>36</v>
       </c>
       <c r="G216" s="19">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H216" s="17" t="s">
         <v>37</v>
@@ -8963,7 +8963,7 @@
         <v>36</v>
       </c>
       <c r="G217" s="19">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H217" s="17" t="s">
         <v>37</v>
@@ -8989,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="G218" s="19">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H218" s="17" t="s">
         <v>37</v>
@@ -9015,7 +9015,7 @@
         <v>36</v>
       </c>
       <c r="G219" s="19">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H219" s="17" t="s">
         <v>37</v>
@@ -9041,7 +9041,7 @@
         <v>36</v>
       </c>
       <c r="G220" s="19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H220" s="17" t="s">
         <v>37</v>
@@ -9067,7 +9067,7 @@
         <v>36</v>
       </c>
       <c r="G221" s="19">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H221" s="17" t="s">
         <v>37</v>
@@ -9093,7 +9093,7 @@
         <v>36</v>
       </c>
       <c r="G222" s="19">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H222" s="17" t="s">
         <v>37</v>
@@ -9119,7 +9119,7 @@
         <v>36</v>
       </c>
       <c r="G223" s="19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H223" s="17" t="s">
         <v>37</v>
@@ -9145,7 +9145,7 @@
         <v>36</v>
       </c>
       <c r="G224" s="19">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H224" s="17" t="s">
         <v>37</v>
@@ -9171,7 +9171,7 @@
         <v>36</v>
       </c>
       <c r="G225" s="19">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H225" s="17" t="s">
         <v>37</v>
@@ -9197,7 +9197,7 @@
         <v>36</v>
       </c>
       <c r="G226" s="19">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H226" s="17" t="s">
         <v>37</v>
@@ -9223,7 +9223,7 @@
         <v>36</v>
       </c>
       <c r="G227" s="19">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H227" s="17" t="s">
         <v>37</v>
@@ -9249,7 +9249,7 @@
         <v>36</v>
       </c>
       <c r="G228" s="19">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H228" s="17" t="s">
         <v>37</v>
@@ -9275,7 +9275,7 @@
         <v>36</v>
       </c>
       <c r="G229" s="19">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H229" s="17" t="s">
         <v>37</v>
@@ -9301,7 +9301,7 @@
         <v>36</v>
       </c>
       <c r="G230" s="19">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H230" s="17" t="s">
         <v>37</v>
@@ -9327,7 +9327,7 @@
         <v>36</v>
       </c>
       <c r="G231" s="19">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>37</v>
@@ -9353,7 +9353,7 @@
         <v>36</v>
       </c>
       <c r="G232" s="19">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H232" s="17" t="s">
         <v>37</v>
@@ -9379,7 +9379,7 @@
         <v>36</v>
       </c>
       <c r="G233" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H233" s="17" t="s">
         <v>37</v>
@@ -9405,7 +9405,7 @@
         <v>36</v>
       </c>
       <c r="G234" s="19">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="H234" s="17" t="s">
         <v>37</v>
@@ -9431,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="G235" s="19">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H235" s="17" t="s">
         <v>37</v>
@@ -9457,7 +9457,7 @@
         <v>36</v>
       </c>
       <c r="G236" s="19">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H236" s="17" t="s">
         <v>37</v>
@@ -9483,7 +9483,7 @@
         <v>36</v>
       </c>
       <c r="G237" s="19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H237" s="17" t="s">
         <v>37</v>
@@ -9509,7 +9509,7 @@
         <v>36</v>
       </c>
       <c r="G238" s="19">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H238" s="17" t="s">
         <v>37</v>
@@ -9535,7 +9535,7 @@
         <v>36</v>
       </c>
       <c r="G239" s="19">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H239" s="17" t="s">
         <v>37</v>
@@ -9561,7 +9561,7 @@
         <v>36</v>
       </c>
       <c r="G240" s="19">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H240" s="17" t="s">
         <v>37</v>
@@ -9587,7 +9587,7 @@
         <v>36</v>
       </c>
       <c r="G241" s="19">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H241" s="17" t="s">
         <v>37</v>
@@ -9613,7 +9613,7 @@
         <v>36</v>
       </c>
       <c r="G242" s="19">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H242" s="17" t="s">
         <v>37</v>
@@ -9639,7 +9639,7 @@
         <v>36</v>
       </c>
       <c r="G243" s="19">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H243" s="17" t="s">
         <v>37</v>
@@ -9665,7 +9665,7 @@
         <v>36</v>
       </c>
       <c r="G244" s="19">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H244" s="17" t="s">
         <v>37</v>
@@ -9691,7 +9691,7 @@
         <v>36</v>
       </c>
       <c r="G245" s="19">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H245" s="17" t="s">
         <v>37</v>
@@ -9717,7 +9717,7 @@
         <v>36</v>
       </c>
       <c r="G246" s="19">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H246" s="17" t="s">
         <v>37</v>
@@ -9743,7 +9743,7 @@
         <v>36</v>
       </c>
       <c r="G247" s="19">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H247" s="17" t="s">
         <v>37</v>
@@ -9769,7 +9769,7 @@
         <v>36</v>
       </c>
       <c r="G248" s="19">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H248" s="17" t="s">
         <v>37</v>
@@ -9795,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="G249" s="19">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>37</v>
@@ -9821,7 +9821,7 @@
         <v>36</v>
       </c>
       <c r="G250" s="19">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H250" s="17" t="s">
         <v>37</v>
@@ -9847,7 +9847,7 @@
         <v>36</v>
       </c>
       <c r="G251" s="19">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H251" s="17" t="s">
         <v>37</v>
@@ -9873,7 +9873,7 @@
         <v>36</v>
       </c>
       <c r="G252" s="19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H252" s="17" t="s">
         <v>37</v>
@@ -9899,7 +9899,7 @@
         <v>36</v>
       </c>
       <c r="G253" s="19">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H253" s="17" t="s">
         <v>37</v>
@@ -9925,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="G254" s="19">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H254" s="17" t="s">
         <v>37</v>
@@ -9951,7 +9951,7 @@
         <v>36</v>
       </c>
       <c r="G255" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H255" s="17" t="s">
         <v>37</v>
@@ -9977,7 +9977,7 @@
         <v>36</v>
       </c>
       <c r="G256" s="19">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H256" s="17" t="s">
         <v>37</v>
@@ -10003,7 +10003,7 @@
         <v>36</v>
       </c>
       <c r="G257" s="19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H257" s="17" t="s">
         <v>37</v>
@@ -10029,7 +10029,7 @@
         <v>36</v>
       </c>
       <c r="G258" s="19">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H258" s="17" t="s">
         <v>37</v>
@@ -10055,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="G259" s="19">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H259" s="17" t="s">
         <v>37</v>
@@ -10081,7 +10081,7 @@
         <v>36</v>
       </c>
       <c r="G260" s="19">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H260" s="17" t="s">
         <v>37</v>
@@ -10107,7 +10107,7 @@
         <v>36</v>
       </c>
       <c r="G261" s="19">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H261" s="17" t="s">
         <v>37</v>
@@ -10133,7 +10133,7 @@
         <v>36</v>
       </c>
       <c r="G262" s="19">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>37</v>
@@ -10159,7 +10159,7 @@
         <v>36</v>
       </c>
       <c r="G263" s="19">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>37</v>
@@ -10185,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="G264" s="19">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H264" s="17" t="s">
         <v>37</v>
@@ -10211,7 +10211,7 @@
         <v>36</v>
       </c>
       <c r="G265" s="19">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H265" s="17" t="s">
         <v>37</v>
@@ -10237,7 +10237,7 @@
         <v>36</v>
       </c>
       <c r="G266" s="19">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>37</v>
@@ -10263,7 +10263,7 @@
         <v>36</v>
       </c>
       <c r="G267" s="19">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H267" s="17" t="s">
         <v>37</v>
@@ -10289,7 +10289,7 @@
         <v>36</v>
       </c>
       <c r="G268" s="19">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H268" s="17" t="s">
         <v>37</v>
@@ -10315,7 +10315,7 @@
         <v>36</v>
       </c>
       <c r="G269" s="19">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H269" s="17" t="s">
         <v>37</v>
@@ -10341,7 +10341,7 @@
         <v>36</v>
       </c>
       <c r="G270" s="19">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H270" s="17" t="s">
         <v>37</v>
@@ -10367,7 +10367,7 @@
         <v>36</v>
       </c>
       <c r="G271" s="19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H271" s="17" t="s">
         <v>37</v>
@@ -10393,7 +10393,7 @@
         <v>36</v>
       </c>
       <c r="G272" s="19">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H272" s="17" t="s">
         <v>37</v>
@@ -10419,7 +10419,7 @@
         <v>36</v>
       </c>
       <c r="G273" s="19">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H273" s="17" t="s">
         <v>37</v>
@@ -10445,7 +10445,7 @@
         <v>36</v>
       </c>
       <c r="G274" s="19">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="H274" s="17" t="s">
         <v>37</v>
@@ -10471,7 +10471,7 @@
         <v>36</v>
       </c>
       <c r="G275" s="19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H275" s="17" t="s">
         <v>37</v>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="G276" s="19">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H276" s="17" t="s">
         <v>37</v>
@@ -10523,7 +10523,7 @@
         <v>36</v>
       </c>
       <c r="G277" s="19">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="H277" s="17" t="s">
         <v>37</v>
@@ -10549,7 +10549,7 @@
         <v>36</v>
       </c>
       <c r="G278" s="19">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H278" s="17" t="s">
         <v>37</v>
@@ -10575,7 +10575,7 @@
         <v>36</v>
       </c>
       <c r="G279" s="19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H279" s="17" t="s">
         <v>37</v>
@@ -10601,7 +10601,7 @@
         <v>36</v>
       </c>
       <c r="G280" s="19">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H280" s="17" t="s">
         <v>37</v>
@@ -10627,7 +10627,7 @@
         <v>36</v>
       </c>
       <c r="G281" s="19">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="H281" s="17" t="s">
         <v>37</v>
@@ -10653,7 +10653,7 @@
         <v>36</v>
       </c>
       <c r="G282" s="19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H282" s="17" t="s">
         <v>37</v>
@@ -10705,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="G284" s="19">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H284" s="17" t="s">
         <v>37</v>
@@ -10731,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="G285" s="19">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H285" s="17" t="s">
         <v>37</v>
@@ -10757,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="G286" s="19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H286" s="17" t="s">
         <v>37</v>
@@ -10783,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="G287" s="19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H287" s="17" t="s">
         <v>37</v>
@@ -10809,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="G288" s="19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H288" s="17" t="s">
         <v>37</v>
@@ -10835,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="G289" s="19">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H289" s="17" t="s">
         <v>37</v>
@@ -10861,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="G290" s="19">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H290" s="17" t="s">
         <v>37</v>
@@ -10887,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="G291" s="19">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H291" s="17" t="s">
         <v>37</v>
@@ -10913,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="G292" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H292" s="17" t="s">
         <v>37</v>
@@ -10939,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="G293" s="19">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="H293" s="17" t="s">
         <v>37</v>
@@ -10965,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="G294" s="19">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H294" s="17" t="s">
         <v>37</v>
@@ -10991,7 +10991,7 @@
         <v>36</v>
       </c>
       <c r="G295" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H295" s="17" t="s">
         <v>37</v>
@@ -11017,7 +11017,7 @@
         <v>36</v>
       </c>
       <c r="G296" s="19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H296" s="17" t="s">
         <v>37</v>
@@ -11043,7 +11043,7 @@
         <v>36</v>
       </c>
       <c r="G297" s="19">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H297" s="17" t="s">
         <v>37</v>
@@ -11069,7 +11069,7 @@
         <v>36</v>
       </c>
       <c r="G298" s="19">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H298" s="17" t="s">
         <v>37</v>
@@ -11095,7 +11095,7 @@
         <v>36</v>
       </c>
       <c r="G299" s="19">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H299" s="17" t="s">
         <v>37</v>
@@ -11147,7 +11147,7 @@
         <v>36</v>
       </c>
       <c r="G301" s="19">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H301" s="17" t="s">
         <v>37</v>
@@ -11173,7 +11173,7 @@
         <v>36</v>
       </c>
       <c r="G302" s="19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H302" s="17" t="s">
         <v>37</v>
@@ -11199,7 +11199,7 @@
         <v>36</v>
       </c>
       <c r="G303" s="19">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H303" s="17" t="s">
         <v>37</v>
@@ -11225,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="G304" s="19">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H304" s="17" t="s">
         <v>37</v>
@@ -11251,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="G305" s="19">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H305" s="17" t="s">
         <v>37</v>
@@ -11277,7 +11277,7 @@
         <v>36</v>
       </c>
       <c r="G306" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H306" s="17" t="s">
         <v>37</v>
@@ -11303,7 +11303,7 @@
         <v>36</v>
       </c>
       <c r="G307" s="19">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H307" s="17" t="s">
         <v>37</v>
@@ -11329,7 +11329,7 @@
         <v>36</v>
       </c>
       <c r="G308" s="19">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H308" s="17" t="s">
         <v>37</v>
@@ -11355,7 +11355,7 @@
         <v>36</v>
       </c>
       <c r="G309" s="19">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="H309" s="17" t="s">
         <v>37</v>
@@ -11381,7 +11381,7 @@
         <v>36</v>
       </c>
       <c r="G310" s="19">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H310" s="17" t="s">
         <v>37</v>
@@ -11407,7 +11407,7 @@
         <v>36</v>
       </c>
       <c r="G311" s="19">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H311" s="17" t="s">
         <v>37</v>
@@ -11433,7 +11433,7 @@
         <v>36</v>
       </c>
       <c r="G312" s="19">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H312" s="17" t="s">
         <v>37</v>
@@ -11459,7 +11459,7 @@
         <v>36</v>
       </c>
       <c r="G313" s="19">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H313" s="17" t="s">
         <v>37</v>
@@ -11485,7 +11485,7 @@
         <v>36</v>
       </c>
       <c r="G314" s="19">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H314" s="17" t="s">
         <v>37</v>
@@ -11511,7 +11511,7 @@
         <v>36</v>
       </c>
       <c r="G315" s="19">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H315" s="17" t="s">
         <v>37</v>
@@ -11537,7 +11537,7 @@
         <v>36</v>
       </c>
       <c r="G316" s="19">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H316" s="17" t="s">
         <v>37</v>
@@ -11563,7 +11563,7 @@
         <v>36</v>
       </c>
       <c r="G317" s="19">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H317" s="17" t="s">
         <v>37</v>
@@ -11589,7 +11589,7 @@
         <v>36</v>
       </c>
       <c r="G318" s="19">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H318" s="17" t="s">
         <v>37</v>
@@ -11615,7 +11615,7 @@
         <v>36</v>
       </c>
       <c r="G319" s="19">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="H319" s="17" t="s">
         <v>37</v>
@@ -11641,7 +11641,7 @@
         <v>36</v>
       </c>
       <c r="G320" s="19">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H320" s="17" t="s">
         <v>37</v>
@@ -11667,7 +11667,7 @@
         <v>36</v>
       </c>
       <c r="G321" s="19">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H321" s="17" t="s">
         <v>37</v>
@@ -11693,7 +11693,7 @@
         <v>36</v>
       </c>
       <c r="G322" s="19">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H322" s="17" t="s">
         <v>37</v>
@@ -11719,7 +11719,7 @@
         <v>36</v>
       </c>
       <c r="G323" s="19">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H323" s="17" t="s">
         <v>37</v>
@@ -11745,7 +11745,7 @@
         <v>36</v>
       </c>
       <c r="G324" s="19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H324" s="17" t="s">
         <v>37</v>
@@ -11771,7 +11771,7 @@
         <v>36</v>
       </c>
       <c r="G325" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H325" s="17" t="s">
         <v>37</v>
@@ -11797,7 +11797,7 @@
         <v>36</v>
       </c>
       <c r="G326" s="19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H326" s="17" t="s">
         <v>37</v>
@@ -11823,7 +11823,7 @@
         <v>36</v>
       </c>
       <c r="G327" s="19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H327" s="17" t="s">
         <v>37</v>
@@ -11849,7 +11849,7 @@
         <v>36</v>
       </c>
       <c r="G328" s="19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H328" s="17" t="s">
         <v>37</v>
@@ -11875,7 +11875,7 @@
         <v>36</v>
       </c>
       <c r="G329" s="19">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="H329" s="17" t="s">
         <v>37</v>
@@ -11901,7 +11901,7 @@
         <v>36</v>
       </c>
       <c r="G330" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H330" s="17" t="s">
         <v>37</v>
@@ -11927,7 +11927,7 @@
         <v>36</v>
       </c>
       <c r="G331" s="19">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H331" s="17" t="s">
         <v>37</v>
@@ -11953,7 +11953,7 @@
         <v>36</v>
       </c>
       <c r="G332" s="19">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H332" s="17" t="s">
         <v>37</v>
@@ -11979,7 +11979,7 @@
         <v>36</v>
       </c>
       <c r="G333" s="19">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H333" s="17" t="s">
         <v>37</v>
@@ -12005,7 +12005,7 @@
         <v>36</v>
       </c>
       <c r="G334" s="19">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H334" s="17" t="s">
         <v>37</v>
@@ -12031,7 +12031,7 @@
         <v>36</v>
       </c>
       <c r="G335" s="19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H335" s="17" t="s">
         <v>37</v>
@@ -12057,7 +12057,7 @@
         <v>36</v>
       </c>
       <c r="G336" s="19">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H336" s="17" t="s">
         <v>37</v>
@@ -12083,7 +12083,7 @@
         <v>36</v>
       </c>
       <c r="G337" s="19">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H337" s="17" t="s">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         <v>36</v>
       </c>
       <c r="G338" s="19">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="H338" s="17" t="s">
         <v>37</v>
@@ -12135,7 +12135,7 @@
         <v>36</v>
       </c>
       <c r="G339" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H339" s="17" t="s">
         <v>37</v>
@@ -12161,7 +12161,7 @@
         <v>36</v>
       </c>
       <c r="G340" s="19">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H340" s="17" t="s">
         <v>37</v>
@@ -12187,7 +12187,7 @@
         <v>36</v>
       </c>
       <c r="G341" s="19">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H341" s="17" t="s">
         <v>37</v>
@@ -12213,7 +12213,7 @@
         <v>36</v>
       </c>
       <c r="G342" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H342" s="17" t="s">
         <v>37</v>
@@ -12239,7 +12239,7 @@
         <v>36</v>
       </c>
       <c r="G343" s="19">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H343" s="17" t="s">
         <v>37</v>
@@ -12265,7 +12265,7 @@
         <v>36</v>
       </c>
       <c r="G344" s="19">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="H344" s="17" t="s">
         <v>37</v>
@@ -12291,7 +12291,7 @@
         <v>36</v>
       </c>
       <c r="G345" s="19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H345" s="17" t="s">
         <v>37</v>
@@ -12317,7 +12317,7 @@
         <v>36</v>
       </c>
       <c r="G346" s="19">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H346" s="17" t="s">
         <v>37</v>
@@ -12343,7 +12343,7 @@
         <v>36</v>
       </c>
       <c r="G347" s="19">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H347" s="17" t="s">
         <v>37</v>
@@ -12369,7 +12369,7 @@
         <v>36</v>
       </c>
       <c r="G348" s="19">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H348" s="17" t="s">
         <v>37</v>
@@ -12395,7 +12395,7 @@
         <v>36</v>
       </c>
       <c r="G349" s="19">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H349" s="17" t="s">
         <v>37</v>
@@ -12421,7 +12421,7 @@
         <v>36</v>
       </c>
       <c r="G350" s="19">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H350" s="17" t="s">
         <v>37</v>
@@ -12447,7 +12447,7 @@
         <v>36</v>
       </c>
       <c r="G351" s="19">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H351" s="17" t="s">
         <v>37</v>
@@ -12473,7 +12473,7 @@
         <v>36</v>
       </c>
       <c r="G352" s="19">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H352" s="17" t="s">
         <v>37</v>
@@ -12499,7 +12499,7 @@
         <v>36</v>
       </c>
       <c r="G353" s="19">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H353" s="17" t="s">
         <v>37</v>
@@ -12525,7 +12525,7 @@
         <v>36</v>
       </c>
       <c r="G354" s="19">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H354" s="17" t="s">
         <v>37</v>
@@ -12551,7 +12551,7 @@
         <v>36</v>
       </c>
       <c r="G355" s="19">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H355" s="17" t="s">
         <v>37</v>
@@ -12577,7 +12577,7 @@
         <v>36</v>
       </c>
       <c r="G356" s="19">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H356" s="17" t="s">
         <v>37</v>
@@ -12603,7 +12603,7 @@
         <v>36</v>
       </c>
       <c r="G357" s="19">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H357" s="17" t="s">
         <v>37</v>
@@ -12629,7 +12629,7 @@
         <v>36</v>
       </c>
       <c r="G358" s="19">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H358" s="17" t="s">
         <v>37</v>
@@ -12655,7 +12655,7 @@
         <v>36</v>
       </c>
       <c r="G359" s="19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H359" s="17" t="s">
         <v>37</v>
@@ -12681,7 +12681,7 @@
         <v>36</v>
       </c>
       <c r="G360" s="19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H360" s="17" t="s">
         <v>37</v>
@@ -12707,7 +12707,7 @@
         <v>36</v>
       </c>
       <c r="G361" s="19">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H361" s="17" t="s">
         <v>37</v>
@@ -12733,7 +12733,7 @@
         <v>36</v>
       </c>
       <c r="G362" s="19">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="H362" s="17" t="s">
         <v>37</v>
@@ -12759,7 +12759,7 @@
         <v>36</v>
       </c>
       <c r="G363" s="19">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H363" s="17" t="s">
         <v>37</v>
@@ -12785,7 +12785,7 @@
         <v>36</v>
       </c>
       <c r="G364" s="19">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H364" s="17" t="s">
         <v>37</v>
@@ -12811,7 +12811,7 @@
         <v>36</v>
       </c>
       <c r="G365" s="19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H365" s="17" t="s">
         <v>37</v>
@@ -12837,7 +12837,7 @@
         <v>36</v>
       </c>
       <c r="G366" s="19">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H366" s="17" t="s">
         <v>37</v>
@@ -12863,7 +12863,7 @@
         <v>36</v>
       </c>
       <c r="G367" s="19">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H367" s="17" t="s">
         <v>37</v>
@@ -12889,7 +12889,7 @@
         <v>36</v>
       </c>
       <c r="G368" s="19">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H368" s="17" t="s">
         <v>37</v>
@@ -12915,7 +12915,7 @@
         <v>36</v>
       </c>
       <c r="G369" s="19">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="H369" s="17" t="s">
         <v>37</v>
@@ -12941,7 +12941,7 @@
         <v>36</v>
       </c>
       <c r="G370" s="19">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H370" s="17" t="s">
         <v>37</v>
@@ -12967,7 +12967,7 @@
         <v>36</v>
       </c>
       <c r="G371" s="19">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H371" s="17" t="s">
         <v>37</v>
@@ -12993,7 +12993,7 @@
         <v>36</v>
       </c>
       <c r="G372" s="19">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H372" s="17" t="s">
         <v>37</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="G373" s="19">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H373" s="17" t="s">
         <v>37</v>
@@ -13045,7 +13045,7 @@
         <v>36</v>
       </c>
       <c r="G374" s="19">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H374" s="17" t="s">
         <v>37</v>
@@ -13071,7 +13071,7 @@
         <v>36</v>
       </c>
       <c r="G375" s="19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H375" s="17" t="s">
         <v>37</v>
@@ -13097,7 +13097,7 @@
         <v>36</v>
       </c>
       <c r="G376" s="19">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H376" s="17" t="s">
         <v>37</v>
@@ -13123,7 +13123,7 @@
         <v>36</v>
       </c>
       <c r="G377" s="19">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H377" s="17" t="s">
         <v>37</v>
@@ -13149,7 +13149,7 @@
         <v>36</v>
       </c>
       <c r="G378" s="19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H378" s="17" t="s">
         <v>37</v>
@@ -13175,7 +13175,7 @@
         <v>36</v>
       </c>
       <c r="G379" s="19">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H379" s="17" t="s">
         <v>37</v>
@@ -13201,7 +13201,7 @@
         <v>36</v>
       </c>
       <c r="G380" s="19">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H380" s="17" t="s">
         <v>37</v>
@@ -13227,7 +13227,7 @@
         <v>36</v>
       </c>
       <c r="G381" s="19">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H381" s="17" t="s">
         <v>37</v>
@@ -13253,7 +13253,7 @@
         <v>36</v>
       </c>
       <c r="G382" s="19">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H382" s="17" t="s">
         <v>37</v>
@@ -13279,7 +13279,7 @@
         <v>36</v>
       </c>
       <c r="G383" s="19">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H383" s="17" t="s">
         <v>37</v>
@@ -13305,7 +13305,7 @@
         <v>36</v>
       </c>
       <c r="G384" s="19">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H384" s="17" t="s">
         <v>37</v>
@@ -13331,7 +13331,7 @@
         <v>36</v>
       </c>
       <c r="G385" s="19">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="H385" s="17" t="s">
         <v>37</v>
@@ -13357,7 +13357,7 @@
         <v>36</v>
       </c>
       <c r="G386" s="19">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H386" s="17" t="s">
         <v>37</v>
@@ -13383,7 +13383,7 @@
         <v>36</v>
       </c>
       <c r="G387" s="19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H387" s="17" t="s">
         <v>37</v>
@@ -13409,7 +13409,7 @@
         <v>36</v>
       </c>
       <c r="G388" s="19">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="H388" s="17" t="s">
         <v>37</v>
@@ -13435,7 +13435,7 @@
         <v>36</v>
       </c>
       <c r="G389" s="19">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="H389" s="17" t="s">
         <v>37</v>
@@ -13461,7 +13461,7 @@
         <v>36</v>
       </c>
       <c r="G390" s="19">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H390" s="17" t="s">
         <v>37</v>
@@ -13513,7 +13513,7 @@
         <v>36</v>
       </c>
       <c r="G392" s="19">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H392" s="17" t="s">
         <v>37</v>
@@ -13539,7 +13539,7 @@
         <v>36</v>
       </c>
       <c r="G393" s="19">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H393" s="17" t="s">
         <v>37</v>
@@ -13591,7 +13591,7 @@
         <v>36</v>
       </c>
       <c r="G395" s="19">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H395" s="17" t="s">
         <v>37</v>
@@ -13617,7 +13617,7 @@
         <v>36</v>
       </c>
       <c r="G396" s="19">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H396" s="17" t="s">
         <v>37</v>
@@ -13643,7 +13643,7 @@
         <v>36</v>
       </c>
       <c r="G397" s="19">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H397" s="17" t="s">
         <v>37</v>
@@ -13669,7 +13669,7 @@
         <v>36</v>
       </c>
       <c r="G398" s="19">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H398" s="17" t="s">
         <v>37</v>
@@ -13695,7 +13695,7 @@
         <v>36</v>
       </c>
       <c r="G399" s="19">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="H399" s="17" t="s">
         <v>37</v>
@@ -13721,7 +13721,7 @@
         <v>36</v>
       </c>
       <c r="G400" s="19">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H400" s="17" t="s">
         <v>37</v>
@@ -13747,7 +13747,7 @@
         <v>36</v>
       </c>
       <c r="G401" s="19">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H401" s="17" t="s">
         <v>37</v>

--- a/web-reports/selenium-test-report.xlsx
+++ b/web-reports/selenium-test-report.xlsx
@@ -83,13 +83,13 @@
     <t>Date &amp; Time</t>
   </si>
   <si>
-    <t>7/22/2026, 10:59:15 AM</t>
+    <t>7/23/2026, 8:51:38 AM</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>14.09 seconds</t>
+    <t>14.52 seconds</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -3373,7 +3373,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="19">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>37</v>
@@ -3399,7 +3399,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>37</v>
@@ -3425,7 +3425,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="19">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>37</v>
@@ -3451,7 +3451,7 @@
         <v>36</v>
       </c>
       <c r="G5" s="19">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>37</v>
@@ -3477,7 +3477,7 @@
         <v>36</v>
       </c>
       <c r="G6" s="19">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>37</v>
@@ -3503,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="G7" s="19">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>37</v>
@@ -3529,7 +3529,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="19">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>37</v>
@@ -3555,7 +3555,7 @@
         <v>36</v>
       </c>
       <c r="G9" s="19">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>37</v>
@@ -3581,7 +3581,7 @@
         <v>36</v>
       </c>
       <c r="G10" s="19">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>37</v>
@@ -3607,7 +3607,7 @@
         <v>36</v>
       </c>
       <c r="G11" s="19">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>37</v>
@@ -3633,7 +3633,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="19">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>37</v>
@@ -3659,7 +3659,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>37</v>
@@ -3685,7 +3685,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="19">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>37</v>
@@ -3711,7 +3711,7 @@
         <v>36</v>
       </c>
       <c r="G15" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>37</v>
@@ -3737,7 +3737,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="19">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="H16" s="17" t="s">
         <v>37</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="19">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="H17" s="17" t="s">
         <v>37</v>
@@ -3789,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="19">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>37</v>
@@ -3815,7 +3815,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="19">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>37</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>37</v>
@@ -3867,7 +3867,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="19">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>37</v>
@@ -3893,7 +3893,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H22" s="17" t="s">
         <v>37</v>
@@ -3919,7 +3919,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="19">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="H23" s="17" t="s">
         <v>37</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="19">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H24" s="17" t="s">
         <v>37</v>
@@ -3971,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="19">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>37</v>
@@ -3997,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="19">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H26" s="17" t="s">
         <v>37</v>
@@ -4023,7 +4023,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="19">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>37</v>
@@ -4049,7 +4049,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="19">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H28" s="17" t="s">
         <v>37</v>
@@ -4075,7 +4075,7 @@
         <v>36</v>
       </c>
       <c r="G29" s="19">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>37</v>
@@ -4101,7 +4101,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="19">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>37</v>
@@ -4153,7 +4153,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="19">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>37</v>
@@ -4179,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="19">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>37</v>
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>37</v>
@@ -4231,7 +4231,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="19">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>37</v>
@@ -4257,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="19">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>37</v>
@@ -4283,7 +4283,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="19">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>37</v>
@@ -4309,7 +4309,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>37</v>
@@ -4335,7 +4335,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="19">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>37</v>
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="19">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H40" s="17" t="s">
         <v>37</v>
@@ -4387,7 +4387,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="19">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>37</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H42" s="17" t="s">
         <v>37</v>
@@ -4439,7 +4439,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="19">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H43" s="17" t="s">
         <v>37</v>
@@ -4465,7 +4465,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H44" s="17" t="s">
         <v>37</v>
@@ -4491,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="19">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H45" s="17" t="s">
         <v>37</v>
@@ -4517,7 +4517,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="19">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H46" s="17" t="s">
         <v>37</v>
@@ -4543,7 +4543,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="19">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H47" s="17" t="s">
         <v>37</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="19">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="H48" s="17" t="s">
         <v>37</v>
@@ -4621,7 +4621,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H50" s="17" t="s">
         <v>37</v>
@@ -4647,7 +4647,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="19">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H51" s="17" t="s">
         <v>37</v>
@@ -4673,7 +4673,7 @@
         <v>36</v>
       </c>
       <c r="G52" s="19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H52" s="17" t="s">
         <v>37</v>
@@ -4699,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="G53" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H53" s="17" t="s">
         <v>37</v>
@@ -4725,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="G54" s="19">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H54" s="17" t="s">
         <v>37</v>
@@ -4751,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="G55" s="19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H55" s="17" t="s">
         <v>37</v>
@@ -4777,7 +4777,7 @@
         <v>36</v>
       </c>
       <c r="G56" s="19">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H56" s="17" t="s">
         <v>37</v>
@@ -4803,7 +4803,7 @@
         <v>36</v>
       </c>
       <c r="G57" s="19">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H57" s="17" t="s">
         <v>37</v>
@@ -4829,7 +4829,7 @@
         <v>36</v>
       </c>
       <c r="G58" s="19">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H58" s="17" t="s">
         <v>37</v>
@@ -4855,7 +4855,7 @@
         <v>36</v>
       </c>
       <c r="G59" s="19">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H59" s="17" t="s">
         <v>37</v>
@@ -4881,7 +4881,7 @@
         <v>36</v>
       </c>
       <c r="G60" s="19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H60" s="17" t="s">
         <v>37</v>
@@ -4907,7 +4907,7 @@
         <v>36</v